--- a/doc/Journal-de-Travail_KirilBormin.xlsx
+++ b/doc/Journal-de-Travail_KirilBormin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\GitHub\ShootMeUp\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3F4280-2288-4254-9668-AA3118763CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9DC4C-7647-4BC2-96FF-2B9EC61C6CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="90">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -308,6 +308,15 @@
   </si>
   <si>
     <t>Maintenant l'objet (p ex. l'ennemie) s'appatait  une fois par soit 100, soit 200, soit 300 frames</t>
+  </si>
+  <si>
+    <t>Changement mineurs dans le code</t>
+  </si>
+  <si>
+    <t>Documentation du rapport</t>
+  </si>
+  <si>
+    <t>J'ai ajouter toutes les sections requises dans le rapport.</t>
   </si>
 </sst>
 </file>
@@ -1260,13 +1269,13 @@
                   <c:v>135</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1590</c:v>
+                  <c:v>1610</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1330,7 +1339,6 @@
     </c:legend>
     <c:plotVisOnly val="0"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1338,6 +1346,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1677,7 +1686,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1685,6 +1693,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2109,16 +2118,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7.7809798270893377E-2</c:v>
+                  <c:v>7.1999999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.91642651296829969</c:v>
+                  <c:v>0.85866666666666669</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.763688760806916E-3</c:v>
+                  <c:v>6.933333333333333E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,7 +2282,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2281,6 +2289,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4303,7 +4312,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O532"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="1" customWidth="1"/>
@@ -4320,7 +4329,7 @@
     <col min="15" max="15" width="11" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
       <c r="B1" s="9"/>
       <c r="C1" s="10"/>
@@ -4331,7 +4340,7 @@
       </c>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:15" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="83" t="s">
         <v>1</v>
       </c>
@@ -4348,14 +4357,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="83" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="83"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>28 heures 55 minutes</v>
+        <v>31 heures 15 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4366,30 +4375,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="23.25" hidden="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:15" ht="23.25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>720</v>
+        <v>840</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C5" s="82" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="82"/>
     </row>
-    <row r="6" spans="1:15" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>9</v>
       </c>
@@ -4412,7 +4421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="72">
         <f>IF(ISBLANK(B7),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B7))</f>
         <v>35</v>
@@ -4432,7 +4441,7 @@
       </c>
       <c r="G7" s="44"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="73">
         <f>IF(ISBLANK(B8),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B8))</f>
         <v>35</v>
@@ -4461,7 +4470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="74">
         <f>IF(ISBLANK(B9),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B9))</f>
         <v>35</v>
@@ -4490,7 +4499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="73">
         <f>IF(ISBLANK(B10),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B10))</f>
         <v>35</v>
@@ -4519,7 +4528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="74">
         <f>IF(ISBLANK(B11),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B11))</f>
         <v>35</v>
@@ -4548,7 +4557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="73">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
         <v>36</v>
@@ -4574,7 +4583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="74">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
         <v>36</v>
@@ -4600,7 +4609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="73">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
         <v>36</v>
@@ -4626,7 +4635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="74">
         <f>IF(ISBLANK(B15),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B15))</f>
         <v>36</v>
@@ -4652,7 +4661,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="73">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
         <v>36</v>
@@ -4675,7 +4684,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="74">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
         <v>36</v>
@@ -4698,7 +4707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="73">
         <f>IF(ISBLANK(B18),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B18))</f>
         <v>36</v>
@@ -4721,7 +4730,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="110.25" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:15" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A19" s="74">
         <f>IF(ISBLANK(B19),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B19))</f>
         <v>37</v>
@@ -4746,7 +4755,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="73">
         <f>IF(ISBLANK(B20),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B20))</f>
         <v>37</v>
@@ -4766,7 +4775,7 @@
       </c>
       <c r="G20" s="45"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="74">
         <f>IF(ISBLANK(B21),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B21))</f>
         <v>37</v>
@@ -4786,7 +4795,7 @@
       </c>
       <c r="G21" s="46"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="73">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
         <v>37</v>
@@ -4806,7 +4815,7 @@
       </c>
       <c r="G22" s="45"/>
     </row>
-    <row r="23" spans="1:15" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="74">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
         <v>37</v>
@@ -4828,7 +4837,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="73">
         <f>IF(ISBLANK(B24),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B24))</f>
         <v>38</v>
@@ -4850,7 +4859,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="74">
         <f>IF(ISBLANK(B25),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B25))</f>
         <v>38</v>
@@ -4874,7 +4883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="73">
         <f>IF(ISBLANK(B26),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B26))</f>
         <v>38</v>
@@ -4894,7 +4903,7 @@
       </c>
       <c r="G26" s="45"/>
     </row>
-    <row r="27" spans="1:15" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="74">
         <f>IF(ISBLANK(B27),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B27))</f>
         <v>39</v>
@@ -4916,7 +4925,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="73">
         <f>IF(ISBLANK(B28),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B28))</f>
         <v>39</v>
@@ -4938,7 +4947,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="74">
         <f>IF(ISBLANK(B29),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B29))</f>
         <v>39</v>
@@ -4958,7 +4967,7 @@
       </c>
       <c r="G29" s="46"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="73">
         <f>IF(ISBLANK(B30),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B30))</f>
         <v>39</v>
@@ -4978,7 +4987,7 @@
       </c>
       <c r="G30" s="45"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="74">
         <f>IF(ISBLANK(B31),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B31))</f>
         <v>40</v>
@@ -5000,7 +5009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="73">
         <f>IF(ISBLANK(B32),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B32))</f>
         <v>40</v>
@@ -5020,7 +5029,7 @@
       </c>
       <c r="G32" s="45"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="74">
         <f>IF(ISBLANK(B33),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B33))</f>
         <v>40</v>
@@ -5042,7 +5051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="73">
         <f>IF(ISBLANK(B34),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B34))</f>
         <v>40</v>
@@ -5064,7 +5073,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="47.25" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A35" s="74">
         <f>IF(ISBLANK(B35),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B35))</f>
         <v>41</v>
@@ -5088,7 +5097,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="73">
         <f>IF(ISBLANK(B36),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B36))</f>
         <v>41</v>
@@ -5110,7 +5119,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="74">
         <f>IF(ISBLANK(B37),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B37))</f>
         <v>41</v>
@@ -5130,7 +5139,7 @@
       </c>
       <c r="G37" s="46"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="73">
         <f>IF(ISBLANK(B38),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B38))</f>
         <v>43</v>
@@ -5150,7 +5159,7 @@
       </c>
       <c r="G38" s="45"/>
     </row>
-    <row r="39" spans="1:7" ht="47.25" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A39" s="74">
         <f>IF(ISBLANK(B39),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B39))</f>
         <v>43</v>
@@ -5174,7 +5183,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="73">
         <f>IF(ISBLANK(B40),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B40))</f>
         <v>43</v>
@@ -5194,7 +5203,7 @@
       </c>
       <c r="G40" s="45"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="74">
         <f>IF(ISBLANK(B41),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B41))</f>
         <v>43</v>
@@ -5214,7 +5223,7 @@
       </c>
       <c r="G41" s="46"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="73">
         <f>IF(ISBLANK(B42),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B42))</f>
         <v>43</v>
@@ -5234,7 +5243,7 @@
       </c>
       <c r="G42" s="45"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="74">
         <f>IF(ISBLANK(B43),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B43))</f>
         <v>43</v>
@@ -5254,7 +5263,7 @@
       </c>
       <c r="G43" s="46"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="73">
         <f>IF(ISBLANK(B44),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B44))</f>
         <v>43</v>
@@ -5278,7 +5287,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="74">
         <f>IF(ISBLANK(B45),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B45))</f>
         <v>43</v>
@@ -5298,7 +5307,7 @@
       </c>
       <c r="G45" s="46"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="73">
         <f>IF(ISBLANK(B46),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B46))</f>
         <v>43</v>
@@ -5318,7 +5327,7 @@
       </c>
       <c r="G46" s="45"/>
     </row>
-    <row r="47" spans="1:7" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="74">
         <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
         <v>43</v>
@@ -5340,7 +5349,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="73">
         <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
         <v>43</v>
@@ -5360,7 +5369,7 @@
       </c>
       <c r="G48" s="45"/>
     </row>
-    <row r="49" spans="1:7" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="74">
         <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
         <v>43</v>
@@ -5382,31 +5391,49 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A50" s="73" t="str">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="73">
         <f>IF(ISBLANK(B50),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B50))</f>
-        <v/>
-      </c>
-      <c r="B50" s="36"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="36">
+        <v>45959</v>
+      </c>
       <c r="C50" s="37"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="27"/>
+      <c r="D50" s="38">
+        <v>20</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="27" t="s">
+        <v>87</v>
+      </c>
       <c r="G50" s="45"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A51" s="74" t="str">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="74">
         <f>IF(ISBLANK(B51),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B51))</f>
-        <v/>
-      </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="41"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="40">
+        <v>45959</v>
+      </c>
+      <c r="C51" s="41">
+        <v>2</v>
+      </c>
       <c r="D51" s="42"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="46"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="E51" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" s="46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="73" t="str">
         <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
         <v/>
@@ -5418,7 +5445,7 @@
       <c r="F52" s="27"/>
       <c r="G52" s="45"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="74" t="str">
         <f>IF(ISBLANK(B53),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B53))</f>
         <v/>
@@ -5430,7 +5457,7 @@
       <c r="F53" s="27"/>
       <c r="G53" s="46"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="73" t="str">
         <f>IF(ISBLANK(B54),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B54))</f>
         <v/>
@@ -5442,7 +5469,7 @@
       <c r="F54" s="27"/>
       <c r="G54" s="45"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="74" t="str">
         <f>IF(ISBLANK(B55),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B55))</f>
         <v/>
@@ -5454,7 +5481,7 @@
       <c r="F55" s="27"/>
       <c r="G55" s="46"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="73" t="str">
         <f>IF(ISBLANK(B56),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B56))</f>
         <v/>
@@ -5466,7 +5493,7 @@
       <c r="F56" s="13"/>
       <c r="G56" s="45"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="74" t="str">
         <f>IF(ISBLANK(B57),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B57))</f>
         <v/>
@@ -5478,7 +5505,7 @@
       <c r="F57" s="14"/>
       <c r="G57" s="46"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="str">
         <f>IF(ISBLANK(B58),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B58))</f>
         <v/>
@@ -5490,7 +5517,7 @@
       <c r="F58" s="13"/>
       <c r="G58" s="45"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="74" t="str">
         <f>IF(ISBLANK(B59),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B59))</f>
         <v/>
@@ -5502,7 +5529,7 @@
       <c r="F59" s="14"/>
       <c r="G59" s="46"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="73" t="str">
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v/>
@@ -5514,7 +5541,7 @@
       <c r="F60" s="13"/>
       <c r="G60" s="45"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="74" t="str">
         <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
         <v/>
@@ -5526,7 +5553,7 @@
       <c r="F61" s="14"/>
       <c r="G61" s="46"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="73" t="str">
         <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
         <v/>
@@ -5538,7 +5565,7 @@
       <c r="F62" s="13"/>
       <c r="G62" s="45"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="74" t="str">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
         <v/>
@@ -5550,7 +5577,7 @@
       <c r="F63" s="14"/>
       <c r="G63" s="46"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="73" t="str">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
         <v/>
@@ -5562,7 +5589,7 @@
       <c r="F64" s="13"/>
       <c r="G64" s="45"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="74" t="str">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
         <v/>
@@ -5574,7 +5601,7 @@
       <c r="F65" s="14"/>
       <c r="G65" s="46"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="73" t="str">
         <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
         <v/>
@@ -5586,7 +5613,7 @@
       <c r="F66" s="13"/>
       <c r="G66" s="45"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="74" t="str">
         <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
         <v/>
@@ -5598,7 +5625,7 @@
       <c r="F67" s="14"/>
       <c r="G67" s="46"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="73" t="str">
         <f>IF(ISBLANK(B68),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B68))</f>
         <v/>
@@ -5610,7 +5637,7 @@
       <c r="F68" s="13"/>
       <c r="G68" s="45"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="74" t="str">
         <f>IF(ISBLANK(B69),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B69))</f>
         <v/>
@@ -5622,7 +5649,7 @@
       <c r="F69" s="14"/>
       <c r="G69" s="46"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="73" t="str">
         <f>IF(ISBLANK(B70),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B70))</f>
         <v/>
@@ -5634,7 +5661,7 @@
       <c r="F70" s="13"/>
       <c r="G70" s="45"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="74" t="str">
         <f>IF(ISBLANK(B71),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B71))</f>
         <v/>
@@ -5646,7 +5673,7 @@
       <c r="F71" s="14"/>
       <c r="G71" s="46"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="73" t="str">
         <f>IF(ISBLANK(B72),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B72))</f>
         <v/>
@@ -5658,7 +5685,7 @@
       <c r="F72" s="13"/>
       <c r="G72" s="45"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="74" t="str">
         <f>IF(ISBLANK(B73),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B73))</f>
         <v/>
@@ -5670,7 +5697,7 @@
       <c r="F73" s="14"/>
       <c r="G73" s="46"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="73" t="str">
         <f>IF(ISBLANK(B74),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B74))</f>
         <v/>
@@ -5682,7 +5709,7 @@
       <c r="F74" s="13"/>
       <c r="G74" s="45"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="74" t="str">
         <f>IF(ISBLANK(B75),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B75))</f>
         <v/>
@@ -5694,7 +5721,7 @@
       <c r="F75" s="14"/>
       <c r="G75" s="46"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="73" t="str">
         <f>IF(ISBLANK(B76),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B76))</f>
         <v/>
@@ -5706,7 +5733,7 @@
       <c r="F76" s="13"/>
       <c r="G76" s="45"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="74" t="str">
         <f>IF(ISBLANK(B77),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B77))</f>
         <v/>
@@ -5718,7 +5745,7 @@
       <c r="F77" s="14"/>
       <c r="G77" s="46"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="73" t="str">
         <f>IF(ISBLANK(B78),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B78))</f>
         <v/>
@@ -5730,7 +5757,7 @@
       <c r="F78" s="13"/>
       <c r="G78" s="45"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="74" t="str">
         <f>IF(ISBLANK(B79),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B79))</f>
         <v/>
@@ -5742,7 +5769,7 @@
       <c r="F79" s="14"/>
       <c r="G79" s="46"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="73" t="str">
         <f>IF(ISBLANK(B80),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B80))</f>
         <v/>
@@ -5754,7 +5781,7 @@
       <c r="F80" s="13"/>
       <c r="G80" s="45"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="74" t="str">
         <f>IF(ISBLANK(B81),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B81))</f>
         <v/>
@@ -5766,7 +5793,7 @@
       <c r="F81" s="14"/>
       <c r="G81" s="46"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="73" t="str">
         <f>IF(ISBLANK(B82),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B82))</f>
         <v/>
@@ -5778,7 +5805,7 @@
       <c r="F82" s="13"/>
       <c r="G82" s="45"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="74" t="str">
         <f>IF(ISBLANK(B83),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B83))</f>
         <v/>
@@ -5790,7 +5817,7 @@
       <c r="F83" s="14"/>
       <c r="G83" s="46"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="73" t="str">
         <f>IF(ISBLANK(B84),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B84))</f>
         <v/>
@@ -5802,7 +5829,7 @@
       <c r="F84" s="13"/>
       <c r="G84" s="45"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="74" t="str">
         <f>IF(ISBLANK(B85),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B85))</f>
         <v/>
@@ -5814,7 +5841,7 @@
       <c r="F85" s="14"/>
       <c r="G85" s="46"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="73" t="str">
         <f>IF(ISBLANK(B86),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B86))</f>
         <v/>
@@ -5826,7 +5853,7 @@
       <c r="F86" s="13"/>
       <c r="G86" s="45"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="74" t="str">
         <f>IF(ISBLANK(B87),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B87))</f>
         <v/>
@@ -5838,7 +5865,7 @@
       <c r="F87" s="14"/>
       <c r="G87" s="46"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="73" t="str">
         <f>IF(ISBLANK(B88),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B88))</f>
         <v/>
@@ -5850,7 +5877,7 @@
       <c r="F88" s="13"/>
       <c r="G88" s="45"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="74" t="str">
         <f>IF(ISBLANK(B89),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B89))</f>
         <v/>
@@ -5862,7 +5889,7 @@
       <c r="F89" s="14"/>
       <c r="G89" s="46"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="73" t="str">
         <f>IF(ISBLANK(B90),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B90))</f>
         <v/>
@@ -5874,7 +5901,7 @@
       <c r="F90" s="13"/>
       <c r="G90" s="45"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="74" t="str">
         <f>IF(ISBLANK(B91),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B91))</f>
         <v/>
@@ -5886,7 +5913,7 @@
       <c r="F91" s="14"/>
       <c r="G91" s="46"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="73" t="str">
         <f>IF(ISBLANK(B92),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B92))</f>
         <v/>
@@ -5898,7 +5925,7 @@
       <c r="F92" s="13"/>
       <c r="G92" s="45"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="74" t="str">
         <f>IF(ISBLANK(B93),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B93))</f>
         <v/>
@@ -5910,7 +5937,7 @@
       <c r="F93" s="14"/>
       <c r="G93" s="46"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="73" t="str">
         <f>IF(ISBLANK(B94),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B94))</f>
         <v/>
@@ -5922,7 +5949,7 @@
       <c r="F94" s="13"/>
       <c r="G94" s="45"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="74" t="str">
         <f>IF(ISBLANK(B95),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B95))</f>
         <v/>
@@ -5934,7 +5961,7 @@
       <c r="F95" s="14"/>
       <c r="G95" s="46"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="73" t="str">
         <f>IF(ISBLANK(B96),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B96))</f>
         <v/>
@@ -5946,7 +5973,7 @@
       <c r="F96" s="13"/>
       <c r="G96" s="45"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="74" t="str">
         <f>IF(ISBLANK(B97),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B97))</f>
         <v/>
@@ -5958,7 +5985,7 @@
       <c r="F97" s="14"/>
       <c r="G97" s="46"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="73" t="str">
         <f>IF(ISBLANK(B98),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B98))</f>
         <v/>
@@ -5970,7 +5997,7 @@
       <c r="F98" s="13"/>
       <c r="G98" s="45"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="74" t="str">
         <f>IF(ISBLANK(B99),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B99))</f>
         <v/>
@@ -5982,7 +6009,7 @@
       <c r="F99" s="14"/>
       <c r="G99" s="46"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="73" t="str">
         <f>IF(ISBLANK(B100),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B100))</f>
         <v/>
@@ -5994,7 +6021,7 @@
       <c r="F100" s="13"/>
       <c r="G100" s="45"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="74" t="str">
         <f>IF(ISBLANK(B101),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B101))</f>
         <v/>
@@ -6006,7 +6033,7 @@
       <c r="F101" s="14"/>
       <c r="G101" s="46"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="73" t="str">
         <f>IF(ISBLANK(B102),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B102))</f>
         <v/>
@@ -6018,7 +6045,7 @@
       <c r="F102" s="13"/>
       <c r="G102" s="45"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="74" t="str">
         <f>IF(ISBLANK(B103),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B103))</f>
         <v/>
@@ -6030,7 +6057,7 @@
       <c r="F103" s="14"/>
       <c r="G103" s="46"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="73" t="str">
         <f>IF(ISBLANK(B104),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B104))</f>
         <v/>
@@ -6042,7 +6069,7 @@
       <c r="F104" s="13"/>
       <c r="G104" s="45"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="74" t="str">
         <f>IF(ISBLANK(B105),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B105))</f>
         <v/>
@@ -6054,7 +6081,7 @@
       <c r="F105" s="14"/>
       <c r="G105" s="46"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="73" t="str">
         <f>IF(ISBLANK(B106),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B106))</f>
         <v/>
@@ -6066,7 +6093,7 @@
       <c r="F106" s="13"/>
       <c r="G106" s="45"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="74" t="str">
         <f>IF(ISBLANK(B107),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B107))</f>
         <v/>
@@ -6078,7 +6105,7 @@
       <c r="F107" s="14"/>
       <c r="G107" s="46"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="73" t="str">
         <f>IF(ISBLANK(B108),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B108))</f>
         <v/>
@@ -6090,7 +6117,7 @@
       <c r="F108" s="13"/>
       <c r="G108" s="45"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="74" t="str">
         <f>IF(ISBLANK(B109),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B109))</f>
         <v/>
@@ -6102,7 +6129,7 @@
       <c r="F109" s="14"/>
       <c r="G109" s="46"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="73" t="str">
         <f>IF(ISBLANK(B110),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B110))</f>
         <v/>
@@ -6114,7 +6141,7 @@
       <c r="F110" s="13"/>
       <c r="G110" s="45"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="74" t="str">
         <f>IF(ISBLANK(B111),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B111))</f>
         <v/>
@@ -6126,7 +6153,7 @@
       <c r="F111" s="14"/>
       <c r="G111" s="46"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="73" t="str">
         <f>IF(ISBLANK(B112),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B112))</f>
         <v/>
@@ -6138,7 +6165,7 @@
       <c r="F112" s="13"/>
       <c r="G112" s="45"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="74" t="str">
         <f>IF(ISBLANK(B113),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B113))</f>
         <v/>
@@ -6150,7 +6177,7 @@
       <c r="F113" s="14"/>
       <c r="G113" s="46"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="73" t="str">
         <f>IF(ISBLANK(B114),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B114))</f>
         <v/>
@@ -6162,7 +6189,7 @@
       <c r="F114" s="13"/>
       <c r="G114" s="45"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="74" t="str">
         <f>IF(ISBLANK(B115),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B115))</f>
         <v/>
@@ -6174,7 +6201,7 @@
       <c r="F115" s="14"/>
       <c r="G115" s="46"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="73" t="str">
         <f>IF(ISBLANK(B116),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B116))</f>
         <v/>
@@ -6186,7 +6213,7 @@
       <c r="F116" s="13"/>
       <c r="G116" s="45"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="74" t="str">
         <f>IF(ISBLANK(B117),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B117))</f>
         <v/>
@@ -6198,7 +6225,7 @@
       <c r="F117" s="14"/>
       <c r="G117" s="46"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="73" t="str">
         <f>IF(ISBLANK(B118),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B118))</f>
         <v/>
@@ -6210,7 +6237,7 @@
       <c r="F118" s="13"/>
       <c r="G118" s="45"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="74" t="str">
         <f>IF(ISBLANK(B119),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B119))</f>
         <v/>
@@ -6222,7 +6249,7 @@
       <c r="F119" s="14"/>
       <c r="G119" s="46"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="73" t="str">
         <f>IF(ISBLANK(B120),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B120))</f>
         <v/>
@@ -6234,7 +6261,7 @@
       <c r="F120" s="13"/>
       <c r="G120" s="45"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="74" t="str">
         <f>IF(ISBLANK(B121),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B121))</f>
         <v/>
@@ -6246,7 +6273,7 @@
       <c r="F121" s="14"/>
       <c r="G121" s="46"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="73" t="str">
         <f>IF(ISBLANK(B122),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B122))</f>
         <v/>
@@ -6258,7 +6285,7 @@
       <c r="F122" s="13"/>
       <c r="G122" s="45"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="74" t="str">
         <f>IF(ISBLANK(B123),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B123))</f>
         <v/>
@@ -6270,7 +6297,7 @@
       <c r="F123" s="14"/>
       <c r="G123" s="46"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="73" t="str">
         <f>IF(ISBLANK(B124),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B124))</f>
         <v/>
@@ -6282,7 +6309,7 @@
       <c r="F124" s="13"/>
       <c r="G124" s="45"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="74" t="str">
         <f>IF(ISBLANK(B125),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B125))</f>
         <v/>
@@ -6294,7 +6321,7 @@
       <c r="F125" s="14"/>
       <c r="G125" s="46"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="73" t="str">
         <f>IF(ISBLANK(B126),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B126))</f>
         <v/>
@@ -6306,7 +6333,7 @@
       <c r="F126" s="13"/>
       <c r="G126" s="45"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="74" t="str">
         <f>IF(ISBLANK(B127),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B127))</f>
         <v/>
@@ -6318,7 +6345,7 @@
       <c r="F127" s="14"/>
       <c r="G127" s="46"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="73" t="str">
         <f>IF(ISBLANK(B128),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B128))</f>
         <v/>
@@ -6330,7 +6357,7 @@
       <c r="F128" s="13"/>
       <c r="G128" s="45"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="74" t="str">
         <f>IF(ISBLANK(B129),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B129))</f>
         <v/>
@@ -6342,7 +6369,7 @@
       <c r="F129" s="14"/>
       <c r="G129" s="46"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="73" t="str">
         <f>IF(ISBLANK(B130),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B130))</f>
         <v/>
@@ -6354,7 +6381,7 @@
       <c r="F130" s="13"/>
       <c r="G130" s="45"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="74" t="str">
         <f>IF(ISBLANK(B131),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B131))</f>
         <v/>
@@ -6366,7 +6393,7 @@
       <c r="F131" s="14"/>
       <c r="G131" s="46"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="73" t="str">
         <f>IF(ISBLANK(B132),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B132))</f>
         <v/>
@@ -6378,7 +6405,7 @@
       <c r="F132" s="13"/>
       <c r="G132" s="45"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="74" t="str">
         <f>IF(ISBLANK(B133),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B133))</f>
         <v/>
@@ -6390,7 +6417,7 @@
       <c r="F133" s="14"/>
       <c r="G133" s="46"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="73" t="str">
         <f>IF(ISBLANK(B134),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B134))</f>
         <v/>
@@ -6402,7 +6429,7 @@
       <c r="F134" s="13"/>
       <c r="G134" s="45"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="74" t="str">
         <f>IF(ISBLANK(B135),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B135))</f>
         <v/>
@@ -6414,7 +6441,7 @@
       <c r="F135" s="14"/>
       <c r="G135" s="46"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="73" t="str">
         <f>IF(ISBLANK(B136),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B136))</f>
         <v/>
@@ -6426,7 +6453,7 @@
       <c r="F136" s="13"/>
       <c r="G136" s="45"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="74" t="str">
         <f>IF(ISBLANK(B137),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B137))</f>
         <v/>
@@ -6438,7 +6465,7 @@
       <c r="F137" s="14"/>
       <c r="G137" s="46"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="73" t="str">
         <f>IF(ISBLANK(B138),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B138))</f>
         <v/>
@@ -6450,7 +6477,7 @@
       <c r="F138" s="13"/>
       <c r="G138" s="45"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="74" t="str">
         <f>IF(ISBLANK(B139),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B139))</f>
         <v/>
@@ -6462,7 +6489,7 @@
       <c r="F139" s="14"/>
       <c r="G139" s="46"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="73" t="str">
         <f>IF(ISBLANK(B140),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B140))</f>
         <v/>
@@ -6474,7 +6501,7 @@
       <c r="F140" s="13"/>
       <c r="G140" s="45"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="74" t="str">
         <f>IF(ISBLANK(B141),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B141))</f>
         <v/>
@@ -6486,7 +6513,7 @@
       <c r="F141" s="14"/>
       <c r="G141" s="46"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="73" t="str">
         <f>IF(ISBLANK(B142),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B142))</f>
         <v/>
@@ -6498,7 +6525,7 @@
       <c r="F142" s="13"/>
       <c r="G142" s="45"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="74" t="str">
         <f>IF(ISBLANK(B143),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B143))</f>
         <v/>
@@ -6510,7 +6537,7 @@
       <c r="F143" s="14"/>
       <c r="G143" s="46"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="73" t="str">
         <f>IF(ISBLANK(B144),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B144))</f>
         <v/>
@@ -6522,7 +6549,7 @@
       <c r="F144" s="13"/>
       <c r="G144" s="45"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="74" t="str">
         <f>IF(ISBLANK(B145),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B145))</f>
         <v/>
@@ -6534,7 +6561,7 @@
       <c r="F145" s="14"/>
       <c r="G145" s="46"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="73" t="str">
         <f>IF(ISBLANK(B146),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B146))</f>
         <v/>
@@ -6546,7 +6573,7 @@
       <c r="F146" s="13"/>
       <c r="G146" s="45"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="74" t="str">
         <f>IF(ISBLANK(B147),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B147))</f>
         <v/>
@@ -6558,7 +6585,7 @@
       <c r="F147" s="14"/>
       <c r="G147" s="46"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="73" t="str">
         <f>IF(ISBLANK(B148),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B148))</f>
         <v/>
@@ -6570,7 +6597,7 @@
       <c r="F148" s="13"/>
       <c r="G148" s="45"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="74" t="str">
         <f>IF(ISBLANK(B149),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B149))</f>
         <v/>
@@ -6582,7 +6609,7 @@
       <c r="F149" s="14"/>
       <c r="G149" s="46"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="73" t="str">
         <f>IF(ISBLANK(B150),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B150))</f>
         <v/>
@@ -6594,7 +6621,7 @@
       <c r="F150" s="13"/>
       <c r="G150" s="45"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="74" t="str">
         <f>IF(ISBLANK(B151),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B151))</f>
         <v/>
@@ -6606,7 +6633,7 @@
       <c r="F151" s="14"/>
       <c r="G151" s="46"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="73" t="str">
         <f>IF(ISBLANK(B152),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B152))</f>
         <v/>
@@ -6618,7 +6645,7 @@
       <c r="F152" s="13"/>
       <c r="G152" s="45"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="74" t="str">
         <f>IF(ISBLANK(B153),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B153))</f>
         <v/>
@@ -6630,7 +6657,7 @@
       <c r="F153" s="14"/>
       <c r="G153" s="46"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="73" t="str">
         <f>IF(ISBLANK(B154),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B154))</f>
         <v/>
@@ -6642,7 +6669,7 @@
       <c r="F154" s="13"/>
       <c r="G154" s="45"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="74" t="str">
         <f>IF(ISBLANK(B155),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B155))</f>
         <v/>
@@ -6654,7 +6681,7 @@
       <c r="F155" s="14"/>
       <c r="G155" s="46"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="73" t="str">
         <f>IF(ISBLANK(B156),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B156))</f>
         <v/>
@@ -6666,7 +6693,7 @@
       <c r="F156" s="13"/>
       <c r="G156" s="45"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="74" t="str">
         <f>IF(ISBLANK(B157),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B157))</f>
         <v/>
@@ -6678,7 +6705,7 @@
       <c r="F157" s="14"/>
       <c r="G157" s="46"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="73" t="str">
         <f>IF(ISBLANK(B158),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B158))</f>
         <v/>
@@ -6690,7 +6717,7 @@
       <c r="F158" s="13"/>
       <c r="G158" s="45"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="74" t="str">
         <f>IF(ISBLANK(B159),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B159))</f>
         <v/>
@@ -6702,7 +6729,7 @@
       <c r="F159" s="14"/>
       <c r="G159" s="46"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="73" t="str">
         <f>IF(ISBLANK(B160),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B160))</f>
         <v/>
@@ -6714,7 +6741,7 @@
       <c r="F160" s="13"/>
       <c r="G160" s="45"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="74" t="str">
         <f>IF(ISBLANK(B161),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B161))</f>
         <v/>
@@ -6726,7 +6753,7 @@
       <c r="F161" s="14"/>
       <c r="G161" s="46"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="73" t="str">
         <f>IF(ISBLANK(B162),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B162))</f>
         <v/>
@@ -6738,7 +6765,7 @@
       <c r="F162" s="13"/>
       <c r="G162" s="45"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="74" t="str">
         <f>IF(ISBLANK(B163),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B163))</f>
         <v/>
@@ -6750,7 +6777,7 @@
       <c r="F163" s="14"/>
       <c r="G163" s="46"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="73" t="str">
         <f>IF(ISBLANK(B164),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B164))</f>
         <v/>
@@ -6762,7 +6789,7 @@
       <c r="F164" s="13"/>
       <c r="G164" s="45"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="74" t="str">
         <f>IF(ISBLANK(B165),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B165))</f>
         <v/>
@@ -6774,7 +6801,7 @@
       <c r="F165" s="14"/>
       <c r="G165" s="46"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="73" t="str">
         <f>IF(ISBLANK(B166),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B166))</f>
         <v/>
@@ -6786,7 +6813,7 @@
       <c r="F166" s="13"/>
       <c r="G166" s="45"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="74" t="str">
         <f>IF(ISBLANK(B167),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B167))</f>
         <v/>
@@ -6798,7 +6825,7 @@
       <c r="F167" s="14"/>
       <c r="G167" s="46"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="73" t="str">
         <f>IF(ISBLANK(B168),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B168))</f>
         <v/>
@@ -6810,7 +6837,7 @@
       <c r="F168" s="13"/>
       <c r="G168" s="45"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="74" t="str">
         <f>IF(ISBLANK(B169),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B169))</f>
         <v/>
@@ -6822,7 +6849,7 @@
       <c r="F169" s="14"/>
       <c r="G169" s="46"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="73" t="str">
         <f>IF(ISBLANK(B170),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B170))</f>
         <v/>
@@ -6834,7 +6861,7 @@
       <c r="F170" s="13"/>
       <c r="G170" s="45"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="74" t="str">
         <f>IF(ISBLANK(B171),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B171))</f>
         <v/>
@@ -6846,7 +6873,7 @@
       <c r="F171" s="14"/>
       <c r="G171" s="46"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="73" t="str">
         <f>IF(ISBLANK(B172),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B172))</f>
         <v/>
@@ -6858,7 +6885,7 @@
       <c r="F172" s="13"/>
       <c r="G172" s="45"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="74" t="str">
         <f>IF(ISBLANK(B173),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B173))</f>
         <v/>
@@ -6870,7 +6897,7 @@
       <c r="F173" s="14"/>
       <c r="G173" s="46"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="73" t="str">
         <f>IF(ISBLANK(B174),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B174))</f>
         <v/>
@@ -6882,7 +6909,7 @@
       <c r="F174" s="13"/>
       <c r="G174" s="45"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="74" t="str">
         <f>IF(ISBLANK(B175),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B175))</f>
         <v/>
@@ -6894,7 +6921,7 @@
       <c r="F175" s="14"/>
       <c r="G175" s="46"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="73" t="str">
         <f>IF(ISBLANK(B176),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B176))</f>
         <v/>
@@ -6906,7 +6933,7 @@
       <c r="F176" s="13"/>
       <c r="G176" s="45"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="74" t="str">
         <f>IF(ISBLANK(B177),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B177))</f>
         <v/>
@@ -6918,7 +6945,7 @@
       <c r="F177" s="14"/>
       <c r="G177" s="46"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="73" t="str">
         <f>IF(ISBLANK(B178),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B178))</f>
         <v/>
@@ -6930,7 +6957,7 @@
       <c r="F178" s="13"/>
       <c r="G178" s="45"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="74" t="str">
         <f>IF(ISBLANK(B179),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B179))</f>
         <v/>
@@ -6942,7 +6969,7 @@
       <c r="F179" s="14"/>
       <c r="G179" s="46"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="73" t="str">
         <f>IF(ISBLANK(B180),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B180))</f>
         <v/>
@@ -6954,7 +6981,7 @@
       <c r="F180" s="13"/>
       <c r="G180" s="45"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="74" t="str">
         <f>IF(ISBLANK(B181),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B181))</f>
         <v/>
@@ -6966,7 +6993,7 @@
       <c r="F181" s="14"/>
       <c r="G181" s="46"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="73" t="str">
         <f>IF(ISBLANK(B182),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B182))</f>
         <v/>
@@ -6978,7 +7005,7 @@
       <c r="F182" s="13"/>
       <c r="G182" s="45"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="74" t="str">
         <f>IF(ISBLANK(B183),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B183))</f>
         <v/>
@@ -6990,7 +7017,7 @@
       <c r="F183" s="14"/>
       <c r="G183" s="46"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="73" t="str">
         <f>IF(ISBLANK(B184),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B184))</f>
         <v/>
@@ -7002,7 +7029,7 @@
       <c r="F184" s="13"/>
       <c r="G184" s="45"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="74" t="str">
         <f>IF(ISBLANK(B185),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B185))</f>
         <v/>
@@ -7014,7 +7041,7 @@
       <c r="F185" s="14"/>
       <c r="G185" s="46"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="73" t="str">
         <f>IF(ISBLANK(B186),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B186))</f>
         <v/>
@@ -7026,7 +7053,7 @@
       <c r="F186" s="13"/>
       <c r="G186" s="45"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="74" t="str">
         <f>IF(ISBLANK(B187),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B187))</f>
         <v/>
@@ -7038,7 +7065,7 @@
       <c r="F187" s="14"/>
       <c r="G187" s="46"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="73" t="str">
         <f>IF(ISBLANK(B188),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B188))</f>
         <v/>
@@ -7050,7 +7077,7 @@
       <c r="F188" s="13"/>
       <c r="G188" s="45"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="74" t="str">
         <f>IF(ISBLANK(B189),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B189))</f>
         <v/>
@@ -7062,7 +7089,7 @@
       <c r="F189" s="14"/>
       <c r="G189" s="46"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="73" t="str">
         <f>IF(ISBLANK(B190),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B190))</f>
         <v/>
@@ -7074,7 +7101,7 @@
       <c r="F190" s="13"/>
       <c r="G190" s="45"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="74" t="str">
         <f>IF(ISBLANK(B191),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B191))</f>
         <v/>
@@ -7086,7 +7113,7 @@
       <c r="F191" s="14"/>
       <c r="G191" s="46"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="73" t="str">
         <f>IF(ISBLANK(B192),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B192))</f>
         <v/>
@@ -7098,7 +7125,7 @@
       <c r="F192" s="13"/>
       <c r="G192" s="45"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="74" t="str">
         <f>IF(ISBLANK(B193),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B193))</f>
         <v/>
@@ -7110,7 +7137,7 @@
       <c r="F193" s="14"/>
       <c r="G193" s="46"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="73" t="str">
         <f>IF(ISBLANK(B194),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B194))</f>
         <v/>
@@ -7122,7 +7149,7 @@
       <c r="F194" s="13"/>
       <c r="G194" s="45"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="74" t="str">
         <f>IF(ISBLANK(B195),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B195))</f>
         <v/>
@@ -7134,7 +7161,7 @@
       <c r="F195" s="14"/>
       <c r="G195" s="46"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="73" t="str">
         <f>IF(ISBLANK(B196),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B196))</f>
         <v/>
@@ -7146,7 +7173,7 @@
       <c r="F196" s="13"/>
       <c r="G196" s="45"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="74" t="str">
         <f>IF(ISBLANK(B197),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B197))</f>
         <v/>
@@ -7158,7 +7185,7 @@
       <c r="F197" s="14"/>
       <c r="G197" s="46"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="73" t="str">
         <f>IF(ISBLANK(B198),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B198))</f>
         <v/>
@@ -7170,7 +7197,7 @@
       <c r="F198" s="13"/>
       <c r="G198" s="45"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="74" t="str">
         <f>IF(ISBLANK(B199),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B199))</f>
         <v/>
@@ -7182,7 +7209,7 @@
       <c r="F199" s="14"/>
       <c r="G199" s="46"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="73" t="str">
         <f>IF(ISBLANK(B200),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B200))</f>
         <v/>
@@ -7194,7 +7221,7 @@
       <c r="F200" s="13"/>
       <c r="G200" s="45"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="74" t="str">
         <f>IF(ISBLANK(B201),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B201))</f>
         <v/>
@@ -7206,7 +7233,7 @@
       <c r="F201" s="14"/>
       <c r="G201" s="46"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="73" t="str">
         <f>IF(ISBLANK(B202),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B202))</f>
         <v/>
@@ -7218,7 +7245,7 @@
       <c r="F202" s="13"/>
       <c r="G202" s="45"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="74" t="str">
         <f>IF(ISBLANK(B203),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B203))</f>
         <v/>
@@ -7230,7 +7257,7 @@
       <c r="F203" s="14"/>
       <c r="G203" s="46"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="73" t="str">
         <f>IF(ISBLANK(B204),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B204))</f>
         <v/>
@@ -7242,7 +7269,7 @@
       <c r="F204" s="13"/>
       <c r="G204" s="45"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="74" t="str">
         <f>IF(ISBLANK(B205),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B205))</f>
         <v/>
@@ -7254,7 +7281,7 @@
       <c r="F205" s="14"/>
       <c r="G205" s="46"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="73" t="str">
         <f>IF(ISBLANK(B206),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B206))</f>
         <v/>
@@ -7266,7 +7293,7 @@
       <c r="F206" s="13"/>
       <c r="G206" s="45"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="74" t="str">
         <f>IF(ISBLANK(B207),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B207))</f>
         <v/>
@@ -7278,7 +7305,7 @@
       <c r="F207" s="14"/>
       <c r="G207" s="46"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="73" t="str">
         <f>IF(ISBLANK(B208),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B208))</f>
         <v/>
@@ -7290,7 +7317,7 @@
       <c r="F208" s="13"/>
       <c r="G208" s="45"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="74" t="str">
         <f>IF(ISBLANK(B209),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B209))</f>
         <v/>
@@ -7302,7 +7329,7 @@
       <c r="F209" s="14"/>
       <c r="G209" s="46"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="73" t="str">
         <f>IF(ISBLANK(B210),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B210))</f>
         <v/>
@@ -7314,7 +7341,7 @@
       <c r="F210" s="13"/>
       <c r="G210" s="45"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="74" t="str">
         <f>IF(ISBLANK(B211),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B211))</f>
         <v/>
@@ -7326,7 +7353,7 @@
       <c r="F211" s="14"/>
       <c r="G211" s="46"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="73" t="str">
         <f>IF(ISBLANK(B212),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B212))</f>
         <v/>
@@ -7338,7 +7365,7 @@
       <c r="F212" s="13"/>
       <c r="G212" s="45"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="74" t="str">
         <f>IF(ISBLANK(B213),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B213))</f>
         <v/>
@@ -7350,7 +7377,7 @@
       <c r="F213" s="14"/>
       <c r="G213" s="46"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="73" t="str">
         <f>IF(ISBLANK(B214),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B214))</f>
         <v/>
@@ -7362,7 +7389,7 @@
       <c r="F214" s="13"/>
       <c r="G214" s="45"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="74" t="str">
         <f>IF(ISBLANK(B215),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B215))</f>
         <v/>
@@ -7374,7 +7401,7 @@
       <c r="F215" s="14"/>
       <c r="G215" s="46"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="73" t="str">
         <f>IF(ISBLANK(B216),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B216))</f>
         <v/>
@@ -7386,7 +7413,7 @@
       <c r="F216" s="13"/>
       <c r="G216" s="45"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="74" t="str">
         <f>IF(ISBLANK(B217),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B217))</f>
         <v/>
@@ -7398,7 +7425,7 @@
       <c r="F217" s="14"/>
       <c r="G217" s="46"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="73" t="str">
         <f>IF(ISBLANK(B218),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B218))</f>
         <v/>
@@ -7410,7 +7437,7 @@
       <c r="F218" s="13"/>
       <c r="G218" s="45"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="74" t="str">
         <f>IF(ISBLANK(B219),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B219))</f>
         <v/>
@@ -7422,7 +7449,7 @@
       <c r="F219" s="14"/>
       <c r="G219" s="46"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="73" t="str">
         <f>IF(ISBLANK(B220),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B220))</f>
         <v/>
@@ -7434,7 +7461,7 @@
       <c r="F220" s="13"/>
       <c r="G220" s="45"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="74" t="str">
         <f>IF(ISBLANK(B221),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B221))</f>
         <v/>
@@ -7446,7 +7473,7 @@
       <c r="F221" s="14"/>
       <c r="G221" s="46"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="73" t="str">
         <f>IF(ISBLANK(B222),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B222))</f>
         <v/>
@@ -7458,7 +7485,7 @@
       <c r="F222" s="13"/>
       <c r="G222" s="45"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="74" t="str">
         <f>IF(ISBLANK(B223),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B223))</f>
         <v/>
@@ -7470,7 +7497,7 @@
       <c r="F223" s="14"/>
       <c r="G223" s="46"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="73" t="str">
         <f>IF(ISBLANK(B224),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B224))</f>
         <v/>
@@ -7482,7 +7509,7 @@
       <c r="F224" s="13"/>
       <c r="G224" s="45"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="74" t="str">
         <f>IF(ISBLANK(B225),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B225))</f>
         <v/>
@@ -7494,7 +7521,7 @@
       <c r="F225" s="14"/>
       <c r="G225" s="46"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="73" t="str">
         <f>IF(ISBLANK(B226),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B226))</f>
         <v/>
@@ -7506,7 +7533,7 @@
       <c r="F226" s="13"/>
       <c r="G226" s="45"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="74" t="str">
         <f>IF(ISBLANK(B227),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B227))</f>
         <v/>
@@ -7518,7 +7545,7 @@
       <c r="F227" s="14"/>
       <c r="G227" s="46"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="73" t="str">
         <f>IF(ISBLANK(B228),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B228))</f>
         <v/>
@@ -7530,7 +7557,7 @@
       <c r="F228" s="13"/>
       <c r="G228" s="45"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="74" t="str">
         <f>IF(ISBLANK(B229),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B229))</f>
         <v/>
@@ -7542,7 +7569,7 @@
       <c r="F229" s="14"/>
       <c r="G229" s="46"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="73" t="str">
         <f>IF(ISBLANK(B230),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B230))</f>
         <v/>
@@ -7554,7 +7581,7 @@
       <c r="F230" s="13"/>
       <c r="G230" s="45"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="74" t="str">
         <f>IF(ISBLANK(B231),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B231))</f>
         <v/>
@@ -7566,7 +7593,7 @@
       <c r="F231" s="14"/>
       <c r="G231" s="46"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="73" t="str">
         <f>IF(ISBLANK(B232),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B232))</f>
         <v/>
@@ -7578,7 +7605,7 @@
       <c r="F232" s="13"/>
       <c r="G232" s="45"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="74" t="str">
         <f>IF(ISBLANK(B233),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B233))</f>
         <v/>
@@ -7590,7 +7617,7 @@
       <c r="F233" s="14"/>
       <c r="G233" s="46"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="73" t="str">
         <f>IF(ISBLANK(B234),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B234))</f>
         <v/>
@@ -7602,7 +7629,7 @@
       <c r="F234" s="13"/>
       <c r="G234" s="45"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="74" t="str">
         <f>IF(ISBLANK(B235),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B235))</f>
         <v/>
@@ -7614,7 +7641,7 @@
       <c r="F235" s="14"/>
       <c r="G235" s="46"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="73" t="str">
         <f>IF(ISBLANK(B236),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B236))</f>
         <v/>
@@ -7626,7 +7653,7 @@
       <c r="F236" s="13"/>
       <c r="G236" s="45"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="74" t="str">
         <f>IF(ISBLANK(B237),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B237))</f>
         <v/>
@@ -7638,7 +7665,7 @@
       <c r="F237" s="14"/>
       <c r="G237" s="46"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="73" t="str">
         <f>IF(ISBLANK(B238),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B238))</f>
         <v/>
@@ -7650,7 +7677,7 @@
       <c r="F238" s="13"/>
       <c r="G238" s="45"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="74" t="str">
         <f>IF(ISBLANK(B239),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B239))</f>
         <v/>
@@ -7662,7 +7689,7 @@
       <c r="F239" s="14"/>
       <c r="G239" s="46"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="73" t="str">
         <f>IF(ISBLANK(B240),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B240))</f>
         <v/>
@@ -7674,7 +7701,7 @@
       <c r="F240" s="13"/>
       <c r="G240" s="45"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="74" t="str">
         <f>IF(ISBLANK(B241),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B241))</f>
         <v/>
@@ -7686,7 +7713,7 @@
       <c r="F241" s="14"/>
       <c r="G241" s="46"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="73" t="str">
         <f>IF(ISBLANK(B242),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B242))</f>
         <v/>
@@ -7698,7 +7725,7 @@
       <c r="F242" s="13"/>
       <c r="G242" s="45"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="74" t="str">
         <f>IF(ISBLANK(B243),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B243))</f>
         <v/>
@@ -7710,7 +7737,7 @@
       <c r="F243" s="14"/>
       <c r="G243" s="46"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="73" t="str">
         <f>IF(ISBLANK(B244),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B244))</f>
         <v/>
@@ -7722,7 +7749,7 @@
       <c r="F244" s="13"/>
       <c r="G244" s="45"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="74" t="str">
         <f>IF(ISBLANK(B245),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B245))</f>
         <v/>
@@ -7734,7 +7761,7 @@
       <c r="F245" s="14"/>
       <c r="G245" s="46"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="73" t="str">
         <f>IF(ISBLANK(B246),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B246))</f>
         <v/>
@@ -7746,7 +7773,7 @@
       <c r="F246" s="13"/>
       <c r="G246" s="45"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="74" t="str">
         <f>IF(ISBLANK(B247),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B247))</f>
         <v/>
@@ -7758,7 +7785,7 @@
       <c r="F247" s="14"/>
       <c r="G247" s="46"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="73" t="str">
         <f>IF(ISBLANK(B248),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B248))</f>
         <v/>
@@ -7770,7 +7797,7 @@
       <c r="F248" s="13"/>
       <c r="G248" s="45"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="74" t="str">
         <f>IF(ISBLANK(B249),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B249))</f>
         <v/>
@@ -7782,7 +7809,7 @@
       <c r="F249" s="14"/>
       <c r="G249" s="46"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="73" t="str">
         <f>IF(ISBLANK(B250),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B250))</f>
         <v/>
@@ -7794,7 +7821,7 @@
       <c r="F250" s="13"/>
       <c r="G250" s="45"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="74" t="str">
         <f>IF(ISBLANK(B251),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B251))</f>
         <v/>
@@ -7806,7 +7833,7 @@
       <c r="F251" s="14"/>
       <c r="G251" s="46"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="73" t="str">
         <f>IF(ISBLANK(B252),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B252))</f>
         <v/>
@@ -7818,7 +7845,7 @@
       <c r="F252" s="13"/>
       <c r="G252" s="45"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="74" t="str">
         <f>IF(ISBLANK(B253),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B253))</f>
         <v/>
@@ -7830,7 +7857,7 @@
       <c r="F253" s="14"/>
       <c r="G253" s="46"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="73" t="str">
         <f>IF(ISBLANK(B254),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B254))</f>
         <v/>
@@ -7842,7 +7869,7 @@
       <c r="F254" s="13"/>
       <c r="G254" s="45"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="74" t="str">
         <f>IF(ISBLANK(B255),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B255))</f>
         <v/>
@@ -7854,7 +7881,7 @@
       <c r="F255" s="14"/>
       <c r="G255" s="46"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="73" t="str">
         <f>IF(ISBLANK(B256),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B256))</f>
         <v/>
@@ -7866,7 +7893,7 @@
       <c r="F256" s="13"/>
       <c r="G256" s="45"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="74" t="str">
         <f>IF(ISBLANK(B257),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B257))</f>
         <v/>
@@ -7878,7 +7905,7 @@
       <c r="F257" s="14"/>
       <c r="G257" s="46"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="str">
         <f>IF(ISBLANK(B258),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B258))</f>
         <v/>
@@ -7890,7 +7917,7 @@
       <c r="F258" s="13"/>
       <c r="G258" s="45"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="74" t="str">
         <f>IF(ISBLANK(B259),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B259))</f>
         <v/>
@@ -7902,7 +7929,7 @@
       <c r="F259" s="14"/>
       <c r="G259" s="46"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="73" t="str">
         <f>IF(ISBLANK(B260),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B260))</f>
         <v/>
@@ -7914,7 +7941,7 @@
       <c r="F260" s="13"/>
       <c r="G260" s="45"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="74" t="str">
         <f>IF(ISBLANK(B261),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B261))</f>
         <v/>
@@ -7926,7 +7953,7 @@
       <c r="F261" s="14"/>
       <c r="G261" s="46"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="73" t="str">
         <f>IF(ISBLANK(B262),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B262))</f>
         <v/>
@@ -7938,7 +7965,7 @@
       <c r="F262" s="13"/>
       <c r="G262" s="45"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="74" t="str">
         <f>IF(ISBLANK(B263),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B263))</f>
         <v/>
@@ -7950,7 +7977,7 @@
       <c r="F263" s="14"/>
       <c r="G263" s="46"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="73" t="str">
         <f>IF(ISBLANK(B264),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B264))</f>
         <v/>
@@ -7962,7 +7989,7 @@
       <c r="F264" s="13"/>
       <c r="G264" s="45"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="74" t="str">
         <f>IF(ISBLANK(B265),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B265))</f>
         <v/>
@@ -7974,7 +8001,7 @@
       <c r="F265" s="14"/>
       <c r="G265" s="46"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="73" t="str">
         <f>IF(ISBLANK(B266),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B266))</f>
         <v/>
@@ -7986,7 +8013,7 @@
       <c r="F266" s="13"/>
       <c r="G266" s="45"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="74" t="str">
         <f>IF(ISBLANK(B267),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B267))</f>
         <v/>
@@ -7998,7 +8025,7 @@
       <c r="F267" s="14"/>
       <c r="G267" s="46"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="73" t="str">
         <f>IF(ISBLANK(B268),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B268))</f>
         <v/>
@@ -8010,7 +8037,7 @@
       <c r="F268" s="13"/>
       <c r="G268" s="45"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="74" t="str">
         <f>IF(ISBLANK(B269),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B269))</f>
         <v/>
@@ -8022,7 +8049,7 @@
       <c r="F269" s="14"/>
       <c r="G269" s="46"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="73" t="str">
         <f>IF(ISBLANK(B270),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B270))</f>
         <v/>
@@ -8034,7 +8061,7 @@
       <c r="F270" s="13"/>
       <c r="G270" s="45"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="74" t="str">
         <f>IF(ISBLANK(B271),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B271))</f>
         <v/>
@@ -8046,7 +8073,7 @@
       <c r="F271" s="14"/>
       <c r="G271" s="46"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="73" t="str">
         <f>IF(ISBLANK(B272),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B272))</f>
         <v/>
@@ -8058,7 +8085,7 @@
       <c r="F272" s="13"/>
       <c r="G272" s="45"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="74" t="str">
         <f>IF(ISBLANK(B273),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B273))</f>
         <v/>
@@ -8070,7 +8097,7 @@
       <c r="F273" s="14"/>
       <c r="G273" s="46"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="73" t="str">
         <f>IF(ISBLANK(B274),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B274))</f>
         <v/>
@@ -8082,7 +8109,7 @@
       <c r="F274" s="13"/>
       <c r="G274" s="45"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="74" t="str">
         <f>IF(ISBLANK(B275),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B275))</f>
         <v/>
@@ -8094,7 +8121,7 @@
       <c r="F275" s="14"/>
       <c r="G275" s="46"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="73" t="str">
         <f>IF(ISBLANK(B276),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B276))</f>
         <v/>
@@ -8106,7 +8133,7 @@
       <c r="F276" s="13"/>
       <c r="G276" s="45"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="74" t="str">
         <f>IF(ISBLANK(B277),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B277))</f>
         <v/>
@@ -8118,7 +8145,7 @@
       <c r="F277" s="14"/>
       <c r="G277" s="46"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="73" t="str">
         <f>IF(ISBLANK(B278),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B278))</f>
         <v/>
@@ -8130,7 +8157,7 @@
       <c r="F278" s="13"/>
       <c r="G278" s="45"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="74" t="str">
         <f>IF(ISBLANK(B279),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B279))</f>
         <v/>
@@ -8142,7 +8169,7 @@
       <c r="F279" s="14"/>
       <c r="G279" s="46"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="73" t="str">
         <f>IF(ISBLANK(B280),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B280))</f>
         <v/>
@@ -8154,7 +8181,7 @@
       <c r="F280" s="13"/>
       <c r="G280" s="45"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="74" t="str">
         <f>IF(ISBLANK(B281),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B281))</f>
         <v/>
@@ -8166,7 +8193,7 @@
       <c r="F281" s="14"/>
       <c r="G281" s="46"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="73" t="str">
         <f>IF(ISBLANK(B282),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B282))</f>
         <v/>
@@ -8178,7 +8205,7 @@
       <c r="F282" s="13"/>
       <c r="G282" s="45"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="74" t="str">
         <f>IF(ISBLANK(B283),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B283))</f>
         <v/>
@@ -8190,7 +8217,7 @@
       <c r="F283" s="14"/>
       <c r="G283" s="46"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="73" t="str">
         <f>IF(ISBLANK(B284),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B284))</f>
         <v/>
@@ -8202,7 +8229,7 @@
       <c r="F284" s="13"/>
       <c r="G284" s="45"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="74" t="str">
         <f>IF(ISBLANK(B285),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B285))</f>
         <v/>
@@ -8214,7 +8241,7 @@
       <c r="F285" s="14"/>
       <c r="G285" s="46"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="73" t="str">
         <f>IF(ISBLANK(B286),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B286))</f>
         <v/>
@@ -8226,7 +8253,7 @@
       <c r="F286" s="13"/>
       <c r="G286" s="45"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="74" t="str">
         <f>IF(ISBLANK(B287),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B287))</f>
         <v/>
@@ -8238,7 +8265,7 @@
       <c r="F287" s="14"/>
       <c r="G287" s="46"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="73" t="str">
         <f>IF(ISBLANK(B288),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B288))</f>
         <v/>
@@ -8250,7 +8277,7 @@
       <c r="F288" s="13"/>
       <c r="G288" s="45"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="74" t="str">
         <f>IF(ISBLANK(B289),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B289))</f>
         <v/>
@@ -8262,7 +8289,7 @@
       <c r="F289" s="14"/>
       <c r="G289" s="46"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="73" t="str">
         <f>IF(ISBLANK(B290),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B290))</f>
         <v/>
@@ -8274,7 +8301,7 @@
       <c r="F290" s="13"/>
       <c r="G290" s="45"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="74" t="str">
         <f>IF(ISBLANK(B291),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B291))</f>
         <v/>
@@ -8286,7 +8313,7 @@
       <c r="F291" s="14"/>
       <c r="G291" s="46"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="73" t="str">
         <f>IF(ISBLANK(B292),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B292))</f>
         <v/>
@@ -8298,7 +8325,7 @@
       <c r="F292" s="13"/>
       <c r="G292" s="45"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="74" t="str">
         <f>IF(ISBLANK(B293),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B293))</f>
         <v/>
@@ -8310,7 +8337,7 @@
       <c r="F293" s="14"/>
       <c r="G293" s="46"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="73" t="str">
         <f>IF(ISBLANK(B294),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B294))</f>
         <v/>
@@ -8322,7 +8349,7 @@
       <c r="F294" s="13"/>
       <c r="G294" s="45"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="74" t="str">
         <f>IF(ISBLANK(B295),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B295))</f>
         <v/>
@@ -8334,7 +8361,7 @@
       <c r="F295" s="14"/>
       <c r="G295" s="46"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="73" t="str">
         <f>IF(ISBLANK(B296),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B296))</f>
         <v/>
@@ -8346,7 +8373,7 @@
       <c r="F296" s="13"/>
       <c r="G296" s="45"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="74" t="str">
         <f>IF(ISBLANK(B297),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B297))</f>
         <v/>
@@ -8358,7 +8385,7 @@
       <c r="F297" s="14"/>
       <c r="G297" s="46"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="73" t="str">
         <f>IF(ISBLANK(B298),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B298))</f>
         <v/>
@@ -8370,7 +8397,7 @@
       <c r="F298" s="13"/>
       <c r="G298" s="45"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="74" t="str">
         <f>IF(ISBLANK(B299),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B299))</f>
         <v/>
@@ -8382,7 +8409,7 @@
       <c r="F299" s="14"/>
       <c r="G299" s="46"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="73" t="str">
         <f>IF(ISBLANK(B300),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B300))</f>
         <v/>
@@ -8394,7 +8421,7 @@
       <c r="F300" s="13"/>
       <c r="G300" s="45"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="74" t="str">
         <f>IF(ISBLANK(B301),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B301))</f>
         <v/>
@@ -8406,7 +8433,7 @@
       <c r="F301" s="14"/>
       <c r="G301" s="46"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="73" t="str">
         <f>IF(ISBLANK(B302),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B302))</f>
         <v/>
@@ -8418,7 +8445,7 @@
       <c r="F302" s="13"/>
       <c r="G302" s="45"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="74" t="str">
         <f>IF(ISBLANK(B303),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B303))</f>
         <v/>
@@ -8430,7 +8457,7 @@
       <c r="F303" s="14"/>
       <c r="G303" s="46"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="73" t="str">
         <f>IF(ISBLANK(B304),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B304))</f>
         <v/>
@@ -8442,7 +8469,7 @@
       <c r="F304" s="13"/>
       <c r="G304" s="45"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="74" t="str">
         <f>IF(ISBLANK(B305),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B305))</f>
         <v/>
@@ -8454,7 +8481,7 @@
       <c r="F305" s="14"/>
       <c r="G305" s="46"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="73" t="str">
         <f>IF(ISBLANK(B306),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B306))</f>
         <v/>
@@ -8466,7 +8493,7 @@
       <c r="F306" s="13"/>
       <c r="G306" s="45"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="74" t="str">
         <f>IF(ISBLANK(B307),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B307))</f>
         <v/>
@@ -8478,7 +8505,7 @@
       <c r="F307" s="14"/>
       <c r="G307" s="46"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="73" t="str">
         <f>IF(ISBLANK(B308),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B308))</f>
         <v/>
@@ -8490,7 +8517,7 @@
       <c r="F308" s="13"/>
       <c r="G308" s="45"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="74" t="str">
         <f>IF(ISBLANK(B309),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B309))</f>
         <v/>
@@ -8502,7 +8529,7 @@
       <c r="F309" s="14"/>
       <c r="G309" s="46"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="73" t="str">
         <f>IF(ISBLANK(B310),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B310))</f>
         <v/>
@@ -8514,7 +8541,7 @@
       <c r="F310" s="13"/>
       <c r="G310" s="45"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="74" t="str">
         <f>IF(ISBLANK(B311),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B311))</f>
         <v/>
@@ -8526,7 +8553,7 @@
       <c r="F311" s="14"/>
       <c r="G311" s="46"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="73" t="str">
         <f>IF(ISBLANK(B312),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B312))</f>
         <v/>
@@ -8538,7 +8565,7 @@
       <c r="F312" s="13"/>
       <c r="G312" s="45"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="74" t="str">
         <f>IF(ISBLANK(B313),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B313))</f>
         <v/>
@@ -8550,7 +8577,7 @@
       <c r="F313" s="14"/>
       <c r="G313" s="46"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="73" t="str">
         <f>IF(ISBLANK(B314),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B314))</f>
         <v/>
@@ -8562,7 +8589,7 @@
       <c r="F314" s="13"/>
       <c r="G314" s="45"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="74" t="str">
         <f>IF(ISBLANK(B315),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B315))</f>
         <v/>
@@ -8574,7 +8601,7 @@
       <c r="F315" s="14"/>
       <c r="G315" s="46"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="73" t="str">
         <f>IF(ISBLANK(B316),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B316))</f>
         <v/>
@@ -8586,7 +8613,7 @@
       <c r="F316" s="13"/>
       <c r="G316" s="45"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="74" t="str">
         <f>IF(ISBLANK(B317),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B317))</f>
         <v/>
@@ -8598,7 +8625,7 @@
       <c r="F317" s="14"/>
       <c r="G317" s="46"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="73" t="str">
         <f>IF(ISBLANK(B318),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B318))</f>
         <v/>
@@ -8610,7 +8637,7 @@
       <c r="F318" s="13"/>
       <c r="G318" s="45"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="74" t="str">
         <f>IF(ISBLANK(B319),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B319))</f>
         <v/>
@@ -8622,7 +8649,7 @@
       <c r="F319" s="14"/>
       <c r="G319" s="46"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="73" t="str">
         <f>IF(ISBLANK(B320),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B320))</f>
         <v/>
@@ -8634,7 +8661,7 @@
       <c r="F320" s="13"/>
       <c r="G320" s="45"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="74" t="str">
         <f>IF(ISBLANK(B321),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B321))</f>
         <v/>
@@ -8646,7 +8673,7 @@
       <c r="F321" s="14"/>
       <c r="G321" s="46"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="73" t="str">
         <f>IF(ISBLANK(B322),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B322))</f>
         <v/>
@@ -8658,7 +8685,7 @@
       <c r="F322" s="13"/>
       <c r="G322" s="45"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="74" t="str">
         <f>IF(ISBLANK(B323),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B323))</f>
         <v/>
@@ -8670,7 +8697,7 @@
       <c r="F323" s="14"/>
       <c r="G323" s="46"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="73" t="str">
         <f>IF(ISBLANK(B324),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B324))</f>
         <v/>
@@ -8682,7 +8709,7 @@
       <c r="F324" s="13"/>
       <c r="G324" s="45"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="74" t="str">
         <f>IF(ISBLANK(B325),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B325))</f>
         <v/>
@@ -8694,7 +8721,7 @@
       <c r="F325" s="14"/>
       <c r="G325" s="46"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="73" t="str">
         <f>IF(ISBLANK(B326),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B326))</f>
         <v/>
@@ -8706,7 +8733,7 @@
       <c r="F326" s="13"/>
       <c r="G326" s="45"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="74" t="str">
         <f>IF(ISBLANK(B327),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B327))</f>
         <v/>
@@ -8718,7 +8745,7 @@
       <c r="F327" s="14"/>
       <c r="G327" s="46"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="73" t="str">
         <f>IF(ISBLANK(B328),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B328))</f>
         <v/>
@@ -8730,7 +8757,7 @@
       <c r="F328" s="13"/>
       <c r="G328" s="45"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="74" t="str">
         <f>IF(ISBLANK(B329),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B329))</f>
         <v/>
@@ -8742,7 +8769,7 @@
       <c r="F329" s="14"/>
       <c r="G329" s="46"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="73" t="str">
         <f>IF(ISBLANK(B330),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B330))</f>
         <v/>
@@ -8754,7 +8781,7 @@
       <c r="F330" s="13"/>
       <c r="G330" s="45"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="74" t="str">
         <f>IF(ISBLANK(B331),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B331))</f>
         <v/>
@@ -8766,7 +8793,7 @@
       <c r="F331" s="14"/>
       <c r="G331" s="46"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="73" t="str">
         <f>IF(ISBLANK(B332),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B332))</f>
         <v/>
@@ -8778,7 +8805,7 @@
       <c r="F332" s="13"/>
       <c r="G332" s="45"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="74" t="str">
         <f>IF(ISBLANK(B333),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B333))</f>
         <v/>
@@ -8790,7 +8817,7 @@
       <c r="F333" s="14"/>
       <c r="G333" s="46"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="73" t="str">
         <f>IF(ISBLANK(B334),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B334))</f>
         <v/>
@@ -8802,7 +8829,7 @@
       <c r="F334" s="13"/>
       <c r="G334" s="45"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="74" t="str">
         <f>IF(ISBLANK(B335),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B335))</f>
         <v/>
@@ -8814,7 +8841,7 @@
       <c r="F335" s="14"/>
       <c r="G335" s="46"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="73" t="str">
         <f>IF(ISBLANK(B336),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B336))</f>
         <v/>
@@ -8826,7 +8853,7 @@
       <c r="F336" s="13"/>
       <c r="G336" s="45"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="74" t="str">
         <f>IF(ISBLANK(B337),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B337))</f>
         <v/>
@@ -8838,7 +8865,7 @@
       <c r="F337" s="14"/>
       <c r="G337" s="46"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="73" t="str">
         <f>IF(ISBLANK(B338),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B338))</f>
         <v/>
@@ -8850,7 +8877,7 @@
       <c r="F338" s="13"/>
       <c r="G338" s="45"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="74" t="str">
         <f>IF(ISBLANK(B339),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B339))</f>
         <v/>
@@ -8862,7 +8889,7 @@
       <c r="F339" s="14"/>
       <c r="G339" s="46"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="73" t="str">
         <f>IF(ISBLANK(B340),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B340))</f>
         <v/>
@@ -8874,7 +8901,7 @@
       <c r="F340" s="13"/>
       <c r="G340" s="45"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="74" t="str">
         <f>IF(ISBLANK(B341),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B341))</f>
         <v/>
@@ -8886,7 +8913,7 @@
       <c r="F341" s="14"/>
       <c r="G341" s="46"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="73" t="str">
         <f>IF(ISBLANK(B342),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B342))</f>
         <v/>
@@ -8898,7 +8925,7 @@
       <c r="F342" s="13"/>
       <c r="G342" s="45"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="74" t="str">
         <f>IF(ISBLANK(B343),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B343))</f>
         <v/>
@@ -8910,7 +8937,7 @@
       <c r="F343" s="14"/>
       <c r="G343" s="46"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="73" t="str">
         <f>IF(ISBLANK(B344),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B344))</f>
         <v/>
@@ -8922,7 +8949,7 @@
       <c r="F344" s="13"/>
       <c r="G344" s="45"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="74" t="str">
         <f>IF(ISBLANK(B345),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B345))</f>
         <v/>
@@ -8934,7 +8961,7 @@
       <c r="F345" s="14"/>
       <c r="G345" s="46"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="73" t="str">
         <f>IF(ISBLANK(B346),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B346))</f>
         <v/>
@@ -8946,7 +8973,7 @@
       <c r="F346" s="13"/>
       <c r="G346" s="45"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="74" t="str">
         <f>IF(ISBLANK(B347),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B347))</f>
         <v/>
@@ -8958,7 +8985,7 @@
       <c r="F347" s="14"/>
       <c r="G347" s="46"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="73" t="str">
         <f>IF(ISBLANK(B348),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B348))</f>
         <v/>
@@ -8970,7 +8997,7 @@
       <c r="F348" s="13"/>
       <c r="G348" s="45"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="74" t="str">
         <f>IF(ISBLANK(B349),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B349))</f>
         <v/>
@@ -8982,7 +9009,7 @@
       <c r="F349" s="14"/>
       <c r="G349" s="46"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="73" t="str">
         <f>IF(ISBLANK(B350),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B350))</f>
         <v/>
@@ -8994,7 +9021,7 @@
       <c r="F350" s="13"/>
       <c r="G350" s="45"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="74" t="str">
         <f>IF(ISBLANK(B351),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B351))</f>
         <v/>
@@ -9006,7 +9033,7 @@
       <c r="F351" s="14"/>
       <c r="G351" s="46"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="73" t="str">
         <f>IF(ISBLANK(B352),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B352))</f>
         <v/>
@@ -9018,7 +9045,7 @@
       <c r="F352" s="13"/>
       <c r="G352" s="45"/>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="74" t="str">
         <f>IF(ISBLANK(B353),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B353))</f>
         <v/>
@@ -9030,7 +9057,7 @@
       <c r="F353" s="14"/>
       <c r="G353" s="46"/>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="73" t="str">
         <f>IF(ISBLANK(B354),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B354))</f>
         <v/>
@@ -9042,7 +9069,7 @@
       <c r="F354" s="13"/>
       <c r="G354" s="45"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="74" t="str">
         <f>IF(ISBLANK(B355),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B355))</f>
         <v/>
@@ -9054,7 +9081,7 @@
       <c r="F355" s="14"/>
       <c r="G355" s="46"/>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="73" t="str">
         <f>IF(ISBLANK(B356),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B356))</f>
         <v/>
@@ -9066,7 +9093,7 @@
       <c r="F356" s="13"/>
       <c r="G356" s="45"/>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="74" t="str">
         <f>IF(ISBLANK(B357),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B357))</f>
         <v/>
@@ -9078,7 +9105,7 @@
       <c r="F357" s="14"/>
       <c r="G357" s="46"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="73" t="str">
         <f>IF(ISBLANK(B358),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B358))</f>
         <v/>
@@ -9090,7 +9117,7 @@
       <c r="F358" s="13"/>
       <c r="G358" s="45"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="74" t="str">
         <f>IF(ISBLANK(B359),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B359))</f>
         <v/>
@@ -9102,7 +9129,7 @@
       <c r="F359" s="14"/>
       <c r="G359" s="46"/>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="73" t="str">
         <f>IF(ISBLANK(B360),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B360))</f>
         <v/>
@@ -9114,7 +9141,7 @@
       <c r="F360" s="13"/>
       <c r="G360" s="45"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="74" t="str">
         <f>IF(ISBLANK(B361),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B361))</f>
         <v/>
@@ -9126,7 +9153,7 @@
       <c r="F361" s="14"/>
       <c r="G361" s="46"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="73" t="str">
         <f>IF(ISBLANK(B362),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B362))</f>
         <v/>
@@ -9138,7 +9165,7 @@
       <c r="F362" s="13"/>
       <c r="G362" s="45"/>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="74" t="str">
         <f>IF(ISBLANK(B363),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B363))</f>
         <v/>
@@ -9150,7 +9177,7 @@
       <c r="F363" s="14"/>
       <c r="G363" s="46"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="73" t="str">
         <f>IF(ISBLANK(B364),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B364))</f>
         <v/>
@@ -9162,7 +9189,7 @@
       <c r="F364" s="13"/>
       <c r="G364" s="45"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="74" t="str">
         <f>IF(ISBLANK(B365),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B365))</f>
         <v/>
@@ -9174,7 +9201,7 @@
       <c r="F365" s="14"/>
       <c r="G365" s="46"/>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="73" t="str">
         <f>IF(ISBLANK(B366),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B366))</f>
         <v/>
@@ -9186,7 +9213,7 @@
       <c r="F366" s="13"/>
       <c r="G366" s="45"/>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="74" t="str">
         <f>IF(ISBLANK(B367),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B367))</f>
         <v/>
@@ -9198,7 +9225,7 @@
       <c r="F367" s="14"/>
       <c r="G367" s="46"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="73" t="str">
         <f>IF(ISBLANK(B368),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B368))</f>
         <v/>
@@ -9210,7 +9237,7 @@
       <c r="F368" s="13"/>
       <c r="G368" s="45"/>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="74" t="str">
         <f>IF(ISBLANK(B369),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B369))</f>
         <v/>
@@ -9222,7 +9249,7 @@
       <c r="F369" s="14"/>
       <c r="G369" s="46"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="73" t="str">
         <f>IF(ISBLANK(B370),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B370))</f>
         <v/>
@@ -9234,7 +9261,7 @@
       <c r="F370" s="13"/>
       <c r="G370" s="45"/>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="74" t="str">
         <f>IF(ISBLANK(B371),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B371))</f>
         <v/>
@@ -9246,7 +9273,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="46"/>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="73" t="str">
         <f>IF(ISBLANK(B372),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B372))</f>
         <v/>
@@ -9258,7 +9285,7 @@
       <c r="F372" s="13"/>
       <c r="G372" s="45"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="74" t="str">
         <f>IF(ISBLANK(B373),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B373))</f>
         <v/>
@@ -9270,7 +9297,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="46"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="73" t="str">
         <f>IF(ISBLANK(B374),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B374))</f>
         <v/>
@@ -9282,7 +9309,7 @@
       <c r="F374" s="13"/>
       <c r="G374" s="45"/>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="74" t="str">
         <f>IF(ISBLANK(B375),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B375))</f>
         <v/>
@@ -9294,7 +9321,7 @@
       <c r="F375" s="14"/>
       <c r="G375" s="46"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="73" t="str">
         <f>IF(ISBLANK(B376),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B376))</f>
         <v/>
@@ -9306,7 +9333,7 @@
       <c r="F376" s="13"/>
       <c r="G376" s="45"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="74" t="str">
         <f>IF(ISBLANK(B377),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B377))</f>
         <v/>
@@ -9318,7 +9345,7 @@
       <c r="F377" s="14"/>
       <c r="G377" s="46"/>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="73" t="str">
         <f>IF(ISBLANK(B378),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B378))</f>
         <v/>
@@ -9330,7 +9357,7 @@
       <c r="F378" s="13"/>
       <c r="G378" s="45"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="74" t="str">
         <f>IF(ISBLANK(B379),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B379))</f>
         <v/>
@@ -9342,7 +9369,7 @@
       <c r="F379" s="14"/>
       <c r="G379" s="46"/>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="73" t="str">
         <f>IF(ISBLANK(B380),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B380))</f>
         <v/>
@@ -9354,7 +9381,7 @@
       <c r="F380" s="13"/>
       <c r="G380" s="45"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="74" t="str">
         <f>IF(ISBLANK(B381),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B381))</f>
         <v/>
@@ -9366,7 +9393,7 @@
       <c r="F381" s="14"/>
       <c r="G381" s="46"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="73" t="str">
         <f>IF(ISBLANK(B382),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B382))</f>
         <v/>
@@ -9378,7 +9405,7 @@
       <c r="F382" s="13"/>
       <c r="G382" s="45"/>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="74" t="str">
         <f>IF(ISBLANK(B383),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B383))</f>
         <v/>
@@ -9390,7 +9417,7 @@
       <c r="F383" s="14"/>
       <c r="G383" s="46"/>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="73" t="str">
         <f>IF(ISBLANK(B384),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B384))</f>
         <v/>
@@ -9402,7 +9429,7 @@
       <c r="F384" s="13"/>
       <c r="G384" s="45"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="74" t="str">
         <f>IF(ISBLANK(B385),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B385))</f>
         <v/>
@@ -9414,7 +9441,7 @@
       <c r="F385" s="14"/>
       <c r="G385" s="46"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="73" t="str">
         <f>IF(ISBLANK(B386),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B386))</f>
         <v/>
@@ -9426,7 +9453,7 @@
       <c r="F386" s="13"/>
       <c r="G386" s="45"/>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="74" t="str">
         <f>IF(ISBLANK(B387),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B387))</f>
         <v/>
@@ -9438,7 +9465,7 @@
       <c r="F387" s="14"/>
       <c r="G387" s="46"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="73" t="str">
         <f>IF(ISBLANK(B388),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B388))</f>
         <v/>
@@ -9450,7 +9477,7 @@
       <c r="F388" s="13"/>
       <c r="G388" s="45"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="74" t="str">
         <f>IF(ISBLANK(B389),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B389))</f>
         <v/>
@@ -9462,7 +9489,7 @@
       <c r="F389" s="14"/>
       <c r="G389" s="46"/>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="73" t="str">
         <f>IF(ISBLANK(B390),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B390))</f>
         <v/>
@@ -9474,7 +9501,7 @@
       <c r="F390" s="13"/>
       <c r="G390" s="45"/>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="74" t="str">
         <f>IF(ISBLANK(B391),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B391))</f>
         <v/>
@@ -9486,7 +9513,7 @@
       <c r="F391" s="14"/>
       <c r="G391" s="46"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="73" t="str">
         <f>IF(ISBLANK(B392),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B392))</f>
         <v/>
@@ -9498,7 +9525,7 @@
       <c r="F392" s="13"/>
       <c r="G392" s="45"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="74" t="str">
         <f>IF(ISBLANK(B393),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B393))</f>
         <v/>
@@ -9510,7 +9537,7 @@
       <c r="F393" s="14"/>
       <c r="G393" s="46"/>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="73" t="str">
         <f>IF(ISBLANK(B394),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B394))</f>
         <v/>
@@ -9522,7 +9549,7 @@
       <c r="F394" s="13"/>
       <c r="G394" s="45"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="74" t="str">
         <f>IF(ISBLANK(B395),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B395))</f>
         <v/>
@@ -9534,7 +9561,7 @@
       <c r="F395" s="14"/>
       <c r="G395" s="46"/>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="73" t="str">
         <f>IF(ISBLANK(B396),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B396))</f>
         <v/>
@@ -9546,7 +9573,7 @@
       <c r="F396" s="13"/>
       <c r="G396" s="45"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="74" t="str">
         <f>IF(ISBLANK(B397),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B397))</f>
         <v/>
@@ -9558,7 +9585,7 @@
       <c r="F397" s="14"/>
       <c r="G397" s="46"/>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="73" t="str">
         <f>IF(ISBLANK(B398),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B398))</f>
         <v/>
@@ -9570,7 +9597,7 @@
       <c r="F398" s="13"/>
       <c r="G398" s="45"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="74" t="str">
         <f>IF(ISBLANK(B399),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B399))</f>
         <v/>
@@ -9582,7 +9609,7 @@
       <c r="F399" s="14"/>
       <c r="G399" s="46"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="73" t="str">
         <f>IF(ISBLANK(B400),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B400))</f>
         <v/>
@@ -9594,7 +9621,7 @@
       <c r="F400" s="13"/>
       <c r="G400" s="45"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="74" t="str">
         <f>IF(ISBLANK(B401),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B401))</f>
         <v/>
@@ -9606,7 +9633,7 @@
       <c r="F401" s="14"/>
       <c r="G401" s="46"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="73" t="str">
         <f>IF(ISBLANK(B402),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B402))</f>
         <v/>
@@ -9618,7 +9645,7 @@
       <c r="F402" s="13"/>
       <c r="G402" s="45"/>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="74" t="str">
         <f>IF(ISBLANK(B403),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B403))</f>
         <v/>
@@ -9630,7 +9657,7 @@
       <c r="F403" s="14"/>
       <c r="G403" s="46"/>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="73" t="str">
         <f>IF(ISBLANK(B404),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B404))</f>
         <v/>
@@ -9642,7 +9669,7 @@
       <c r="F404" s="13"/>
       <c r="G404" s="45"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="74" t="str">
         <f>IF(ISBLANK(B405),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B405))</f>
         <v/>
@@ -9654,7 +9681,7 @@
       <c r="F405" s="14"/>
       <c r="G405" s="46"/>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="73" t="str">
         <f>IF(ISBLANK(B406),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B406))</f>
         <v/>
@@ -9666,7 +9693,7 @@
       <c r="F406" s="13"/>
       <c r="G406" s="45"/>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="74" t="str">
         <f>IF(ISBLANK(B407),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B407))</f>
         <v/>
@@ -9678,7 +9705,7 @@
       <c r="F407" s="14"/>
       <c r="G407" s="46"/>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="73" t="str">
         <f>IF(ISBLANK(B408),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B408))</f>
         <v/>
@@ -9690,7 +9717,7 @@
       <c r="F408" s="13"/>
       <c r="G408" s="45"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="74" t="str">
         <f>IF(ISBLANK(B409),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B409))</f>
         <v/>
@@ -9702,7 +9729,7 @@
       <c r="F409" s="14"/>
       <c r="G409" s="46"/>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="73" t="str">
         <f>IF(ISBLANK(B410),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B410))</f>
         <v/>
@@ -9714,7 +9741,7 @@
       <c r="F410" s="13"/>
       <c r="G410" s="45"/>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="74" t="str">
         <f>IF(ISBLANK(B411),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B411))</f>
         <v/>
@@ -9726,7 +9753,7 @@
       <c r="F411" s="14"/>
       <c r="G411" s="46"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="73" t="str">
         <f>IF(ISBLANK(B412),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B412))</f>
         <v/>
@@ -9738,7 +9765,7 @@
       <c r="F412" s="13"/>
       <c r="G412" s="45"/>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="74" t="str">
         <f>IF(ISBLANK(B413),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B413))</f>
         <v/>
@@ -9750,7 +9777,7 @@
       <c r="F413" s="14"/>
       <c r="G413" s="46"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="73" t="str">
         <f>IF(ISBLANK(B414),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B414))</f>
         <v/>
@@ -9762,7 +9789,7 @@
       <c r="F414" s="13"/>
       <c r="G414" s="45"/>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="74" t="str">
         <f>IF(ISBLANK(B415),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B415))</f>
         <v/>
@@ -9774,7 +9801,7 @@
       <c r="F415" s="14"/>
       <c r="G415" s="46"/>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="73" t="str">
         <f>IF(ISBLANK(B416),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B416))</f>
         <v/>
@@ -9786,7 +9813,7 @@
       <c r="F416" s="13"/>
       <c r="G416" s="45"/>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="74" t="str">
         <f>IF(ISBLANK(B417),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B417))</f>
         <v/>
@@ -9798,7 +9825,7 @@
       <c r="F417" s="14"/>
       <c r="G417" s="46"/>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="73" t="str">
         <f>IF(ISBLANK(B418),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B418))</f>
         <v/>
@@ -9810,7 +9837,7 @@
       <c r="F418" s="13"/>
       <c r="G418" s="45"/>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="74" t="str">
         <f>IF(ISBLANK(B419),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B419))</f>
         <v/>
@@ -9822,7 +9849,7 @@
       <c r="F419" s="14"/>
       <c r="G419" s="46"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="73" t="str">
         <f>IF(ISBLANK(B420),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B420))</f>
         <v/>
@@ -9834,7 +9861,7 @@
       <c r="F420" s="13"/>
       <c r="G420" s="45"/>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="74" t="str">
         <f>IF(ISBLANK(B421),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B421))</f>
         <v/>
@@ -9846,7 +9873,7 @@
       <c r="F421" s="14"/>
       <c r="G421" s="46"/>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="73" t="str">
         <f>IF(ISBLANK(B422),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B422))</f>
         <v/>
@@ -9858,7 +9885,7 @@
       <c r="F422" s="13"/>
       <c r="G422" s="45"/>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="74" t="str">
         <f>IF(ISBLANK(B423),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B423))</f>
         <v/>
@@ -9870,7 +9897,7 @@
       <c r="F423" s="14"/>
       <c r="G423" s="46"/>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="73" t="str">
         <f>IF(ISBLANK(B424),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B424))</f>
         <v/>
@@ -9882,7 +9909,7 @@
       <c r="F424" s="13"/>
       <c r="G424" s="45"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="74" t="str">
         <f>IF(ISBLANK(B425),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B425))</f>
         <v/>
@@ -9894,7 +9921,7 @@
       <c r="F425" s="14"/>
       <c r="G425" s="46"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="73" t="str">
         <f>IF(ISBLANK(B426),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B426))</f>
         <v/>
@@ -9906,7 +9933,7 @@
       <c r="F426" s="13"/>
       <c r="G426" s="45"/>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="74" t="str">
         <f>IF(ISBLANK(B427),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B427))</f>
         <v/>
@@ -9918,7 +9945,7 @@
       <c r="F427" s="14"/>
       <c r="G427" s="46"/>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="73" t="str">
         <f>IF(ISBLANK(B428),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B428))</f>
         <v/>
@@ -9930,7 +9957,7 @@
       <c r="F428" s="13"/>
       <c r="G428" s="45"/>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="74" t="str">
         <f>IF(ISBLANK(B429),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B429))</f>
         <v/>
@@ -9942,7 +9969,7 @@
       <c r="F429" s="14"/>
       <c r="G429" s="46"/>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="73" t="str">
         <f>IF(ISBLANK(B430),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B430))</f>
         <v/>
@@ -9954,7 +9981,7 @@
       <c r="F430" s="13"/>
       <c r="G430" s="45"/>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="74" t="str">
         <f>IF(ISBLANK(B431),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B431))</f>
         <v/>
@@ -9966,7 +9993,7 @@
       <c r="F431" s="14"/>
       <c r="G431" s="46"/>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="73" t="str">
         <f>IF(ISBLANK(B432),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B432))</f>
         <v/>
@@ -9978,7 +10005,7 @@
       <c r="F432" s="13"/>
       <c r="G432" s="45"/>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="74" t="str">
         <f>IF(ISBLANK(B433),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B433))</f>
         <v/>
@@ -9990,7 +10017,7 @@
       <c r="F433" s="14"/>
       <c r="G433" s="46"/>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="73" t="str">
         <f>IF(ISBLANK(B434),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B434))</f>
         <v/>
@@ -10002,7 +10029,7 @@
       <c r="F434" s="13"/>
       <c r="G434" s="45"/>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="74" t="str">
         <f>IF(ISBLANK(B435),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B435))</f>
         <v/>
@@ -10014,7 +10041,7 @@
       <c r="F435" s="14"/>
       <c r="G435" s="46"/>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="73" t="str">
         <f>IF(ISBLANK(B436),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B436))</f>
         <v/>
@@ -10026,7 +10053,7 @@
       <c r="F436" s="13"/>
       <c r="G436" s="45"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="74" t="str">
         <f>IF(ISBLANK(B437),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B437))</f>
         <v/>
@@ -10038,7 +10065,7 @@
       <c r="F437" s="14"/>
       <c r="G437" s="46"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="73" t="str">
         <f>IF(ISBLANK(B438),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B438))</f>
         <v/>
@@ -10050,7 +10077,7 @@
       <c r="F438" s="13"/>
       <c r="G438" s="45"/>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="74" t="str">
         <f>IF(ISBLANK(B439),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B439))</f>
         <v/>
@@ -10062,7 +10089,7 @@
       <c r="F439" s="14"/>
       <c r="G439" s="46"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="73" t="str">
         <f>IF(ISBLANK(B440),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B440))</f>
         <v/>
@@ -10074,7 +10101,7 @@
       <c r="F440" s="13"/>
       <c r="G440" s="45"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="74" t="str">
         <f>IF(ISBLANK(B441),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B441))</f>
         <v/>
@@ -10086,7 +10113,7 @@
       <c r="F441" s="14"/>
       <c r="G441" s="46"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="73" t="str">
         <f>IF(ISBLANK(B442),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B442))</f>
         <v/>
@@ -10098,7 +10125,7 @@
       <c r="F442" s="13"/>
       <c r="G442" s="45"/>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="74" t="str">
         <f>IF(ISBLANK(B443),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B443))</f>
         <v/>
@@ -10110,7 +10137,7 @@
       <c r="F443" s="14"/>
       <c r="G443" s="46"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="73" t="str">
         <f>IF(ISBLANK(B444),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B444))</f>
         <v/>
@@ -10122,7 +10149,7 @@
       <c r="F444" s="13"/>
       <c r="G444" s="45"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="74" t="str">
         <f>IF(ISBLANK(B445),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B445))</f>
         <v/>
@@ -10134,7 +10161,7 @@
       <c r="F445" s="14"/>
       <c r="G445" s="46"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="73" t="str">
         <f>IF(ISBLANK(B446),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B446))</f>
         <v/>
@@ -10146,7 +10173,7 @@
       <c r="F446" s="13"/>
       <c r="G446" s="45"/>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="74" t="str">
         <f>IF(ISBLANK(B447),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B447))</f>
         <v/>
@@ -10158,7 +10185,7 @@
       <c r="F447" s="14"/>
       <c r="G447" s="46"/>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="73" t="str">
         <f>IF(ISBLANK(B448),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B448))</f>
         <v/>
@@ -10170,7 +10197,7 @@
       <c r="F448" s="13"/>
       <c r="G448" s="45"/>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="74" t="str">
         <f>IF(ISBLANK(B449),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B449))</f>
         <v/>
@@ -10182,7 +10209,7 @@
       <c r="F449" s="14"/>
       <c r="G449" s="46"/>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="73" t="str">
         <f>IF(ISBLANK(B450),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B450))</f>
         <v/>
@@ -10194,7 +10221,7 @@
       <c r="F450" s="13"/>
       <c r="G450" s="45"/>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="74" t="str">
         <f>IF(ISBLANK(B451),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B451))</f>
         <v/>
@@ -10206,7 +10233,7 @@
       <c r="F451" s="14"/>
       <c r="G451" s="46"/>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="73" t="str">
         <f>IF(ISBLANK(B452),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B452))</f>
         <v/>
@@ -10218,7 +10245,7 @@
       <c r="F452" s="13"/>
       <c r="G452" s="45"/>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="74" t="str">
         <f>IF(ISBLANK(B453),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B453))</f>
         <v/>
@@ -10230,7 +10257,7 @@
       <c r="F453" s="14"/>
       <c r="G453" s="46"/>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="73" t="str">
         <f>IF(ISBLANK(B454),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B454))</f>
         <v/>
@@ -10242,7 +10269,7 @@
       <c r="F454" s="13"/>
       <c r="G454" s="45"/>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="74" t="str">
         <f>IF(ISBLANK(B455),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B455))</f>
         <v/>
@@ -10254,7 +10281,7 @@
       <c r="F455" s="14"/>
       <c r="G455" s="46"/>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="73" t="str">
         <f>IF(ISBLANK(B456),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B456))</f>
         <v/>
@@ -10266,7 +10293,7 @@
       <c r="F456" s="13"/>
       <c r="G456" s="45"/>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="74" t="str">
         <f>IF(ISBLANK(B457),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B457))</f>
         <v/>
@@ -10278,7 +10305,7 @@
       <c r="F457" s="14"/>
       <c r="G457" s="46"/>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="73" t="str">
         <f>IF(ISBLANK(B458),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B458))</f>
         <v/>
@@ -10290,7 +10317,7 @@
       <c r="F458" s="13"/>
       <c r="G458" s="45"/>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="74" t="str">
         <f>IF(ISBLANK(B459),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B459))</f>
         <v/>
@@ -10302,7 +10329,7 @@
       <c r="F459" s="14"/>
       <c r="G459" s="46"/>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="73" t="str">
         <f>IF(ISBLANK(B460),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B460))</f>
         <v/>
@@ -10314,7 +10341,7 @@
       <c r="F460" s="13"/>
       <c r="G460" s="45"/>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="74" t="str">
         <f>IF(ISBLANK(B461),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B461))</f>
         <v/>
@@ -10326,7 +10353,7 @@
       <c r="F461" s="14"/>
       <c r="G461" s="46"/>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="73" t="str">
         <f>IF(ISBLANK(B462),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B462))</f>
         <v/>
@@ -10338,7 +10365,7 @@
       <c r="F462" s="13"/>
       <c r="G462" s="45"/>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="74" t="str">
         <f>IF(ISBLANK(B463),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B463))</f>
         <v/>
@@ -10350,7 +10377,7 @@
       <c r="F463" s="14"/>
       <c r="G463" s="46"/>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="73" t="str">
         <f>IF(ISBLANK(B464),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B464))</f>
         <v/>
@@ -10362,7 +10389,7 @@
       <c r="F464" s="13"/>
       <c r="G464" s="45"/>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="74" t="str">
         <f>IF(ISBLANK(B465),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B465))</f>
         <v/>
@@ -10374,7 +10401,7 @@
       <c r="F465" s="14"/>
       <c r="G465" s="46"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="73" t="str">
         <f>IF(ISBLANK(B466),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B466))</f>
         <v/>
@@ -10386,7 +10413,7 @@
       <c r="F466" s="13"/>
       <c r="G466" s="45"/>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="74" t="str">
         <f>IF(ISBLANK(B467),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B467))</f>
         <v/>
@@ -10398,7 +10425,7 @@
       <c r="F467" s="14"/>
       <c r="G467" s="46"/>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="73" t="str">
         <f>IF(ISBLANK(B468),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B468))</f>
         <v/>
@@ -10410,7 +10437,7 @@
       <c r="F468" s="13"/>
       <c r="G468" s="45"/>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="74" t="str">
         <f>IF(ISBLANK(B469),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B469))</f>
         <v/>
@@ -10422,7 +10449,7 @@
       <c r="F469" s="14"/>
       <c r="G469" s="46"/>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="73" t="str">
         <f>IF(ISBLANK(B470),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B470))</f>
         <v/>
@@ -10434,7 +10461,7 @@
       <c r="F470" s="13"/>
       <c r="G470" s="45"/>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="74" t="str">
         <f>IF(ISBLANK(B471),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B471))</f>
         <v/>
@@ -10446,7 +10473,7 @@
       <c r="F471" s="14"/>
       <c r="G471" s="46"/>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="73" t="str">
         <f>IF(ISBLANK(B472),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B472))</f>
         <v/>
@@ -10458,7 +10485,7 @@
       <c r="F472" s="13"/>
       <c r="G472" s="45"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="74" t="str">
         <f>IF(ISBLANK(B473),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B473))</f>
         <v/>
@@ -10470,7 +10497,7 @@
       <c r="F473" s="14"/>
       <c r="G473" s="46"/>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="73" t="str">
         <f>IF(ISBLANK(B474),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B474))</f>
         <v/>
@@ -10482,7 +10509,7 @@
       <c r="F474" s="13"/>
       <c r="G474" s="45"/>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="74" t="str">
         <f>IF(ISBLANK(B475),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B475))</f>
         <v/>
@@ -10494,7 +10521,7 @@
       <c r="F475" s="14"/>
       <c r="G475" s="46"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="73" t="str">
         <f>IF(ISBLANK(B476),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B476))</f>
         <v/>
@@ -10506,7 +10533,7 @@
       <c r="F476" s="13"/>
       <c r="G476" s="45"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="74" t="str">
         <f>IF(ISBLANK(B477),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B477))</f>
         <v/>
@@ -10518,7 +10545,7 @@
       <c r="F477" s="14"/>
       <c r="G477" s="46"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="73" t="str">
         <f>IF(ISBLANK(B478),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B478))</f>
         <v/>
@@ -10530,7 +10557,7 @@
       <c r="F478" s="13"/>
       <c r="G478" s="45"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="74" t="str">
         <f>IF(ISBLANK(B479),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B479))</f>
         <v/>
@@ -10542,7 +10569,7 @@
       <c r="F479" s="14"/>
       <c r="G479" s="46"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="73" t="str">
         <f>IF(ISBLANK(B480),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B480))</f>
         <v/>
@@ -10554,7 +10581,7 @@
       <c r="F480" s="13"/>
       <c r="G480" s="45"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="74" t="str">
         <f>IF(ISBLANK(B481),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B481))</f>
         <v/>
@@ -10566,7 +10593,7 @@
       <c r="F481" s="14"/>
       <c r="G481" s="46"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="73" t="str">
         <f>IF(ISBLANK(B482),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B482))</f>
         <v/>
@@ -10578,7 +10605,7 @@
       <c r="F482" s="13"/>
       <c r="G482" s="45"/>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="74" t="str">
         <f>IF(ISBLANK(B483),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B483))</f>
         <v/>
@@ -10590,7 +10617,7 @@
       <c r="F483" s="14"/>
       <c r="G483" s="46"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="73" t="str">
         <f>IF(ISBLANK(B484),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B484))</f>
         <v/>
@@ -10602,7 +10629,7 @@
       <c r="F484" s="13"/>
       <c r="G484" s="45"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="74" t="str">
         <f>IF(ISBLANK(B485),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B485))</f>
         <v/>
@@ -10614,7 +10641,7 @@
       <c r="F485" s="14"/>
       <c r="G485" s="46"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="73" t="str">
         <f>IF(ISBLANK(B486),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B486))</f>
         <v/>
@@ -10626,7 +10653,7 @@
       <c r="F486" s="13"/>
       <c r="G486" s="45"/>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="74" t="str">
         <f>IF(ISBLANK(B487),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B487))</f>
         <v/>
@@ -10638,7 +10665,7 @@
       <c r="F487" s="14"/>
       <c r="G487" s="46"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="73" t="str">
         <f>IF(ISBLANK(B488),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B488))</f>
         <v/>
@@ -10650,7 +10677,7 @@
       <c r="F488" s="13"/>
       <c r="G488" s="45"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="74" t="str">
         <f>IF(ISBLANK(B489),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B489))</f>
         <v/>
@@ -10662,7 +10689,7 @@
       <c r="F489" s="14"/>
       <c r="G489" s="46"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="73" t="str">
         <f>IF(ISBLANK(B490),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B490))</f>
         <v/>
@@ -10674,7 +10701,7 @@
       <c r="F490" s="13"/>
       <c r="G490" s="45"/>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="74" t="str">
         <f>IF(ISBLANK(B491),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B491))</f>
         <v/>
@@ -10686,7 +10713,7 @@
       <c r="F491" s="14"/>
       <c r="G491" s="46"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="73" t="str">
         <f>IF(ISBLANK(B492),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B492))</f>
         <v/>
@@ -10698,7 +10725,7 @@
       <c r="F492" s="13"/>
       <c r="G492" s="45"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="74" t="str">
         <f>IF(ISBLANK(B493),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B493))</f>
         <v/>
@@ -10710,7 +10737,7 @@
       <c r="F493" s="14"/>
       <c r="G493" s="46"/>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="73" t="str">
         <f>IF(ISBLANK(B494),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B494))</f>
         <v/>
@@ -10722,7 +10749,7 @@
       <c r="F494" s="13"/>
       <c r="G494" s="45"/>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="74" t="str">
         <f>IF(ISBLANK(B495),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B495))</f>
         <v/>
@@ -10734,7 +10761,7 @@
       <c r="F495" s="14"/>
       <c r="G495" s="46"/>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="73" t="str">
         <f>IF(ISBLANK(B496),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B496))</f>
         <v/>
@@ -10746,7 +10773,7 @@
       <c r="F496" s="13"/>
       <c r="G496" s="45"/>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="74" t="str">
         <f>IF(ISBLANK(B497),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B497))</f>
         <v/>
@@ -10758,7 +10785,7 @@
       <c r="F497" s="14"/>
       <c r="G497" s="46"/>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="73" t="str">
         <f>IF(ISBLANK(B498),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B498))</f>
         <v/>
@@ -10770,7 +10797,7 @@
       <c r="F498" s="13"/>
       <c r="G498" s="45"/>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="74" t="str">
         <f>IF(ISBLANK(B499),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B499))</f>
         <v/>
@@ -10782,7 +10809,7 @@
       <c r="F499" s="14"/>
       <c r="G499" s="46"/>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="73" t="str">
         <f>IF(ISBLANK(B500),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B500))</f>
         <v/>
@@ -10794,7 +10821,7 @@
       <c r="F500" s="13"/>
       <c r="G500" s="45"/>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="74" t="str">
         <f>IF(ISBLANK(B501),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B501))</f>
         <v/>
@@ -10806,7 +10833,7 @@
       <c r="F501" s="14"/>
       <c r="G501" s="46"/>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="73" t="str">
         <f>IF(ISBLANK(B502),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B502))</f>
         <v/>
@@ -10818,7 +10845,7 @@
       <c r="F502" s="13"/>
       <c r="G502" s="45"/>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="74" t="str">
         <f>IF(ISBLANK(B503),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B503))</f>
         <v/>
@@ -10830,7 +10857,7 @@
       <c r="F503" s="14"/>
       <c r="G503" s="46"/>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="73" t="str">
         <f>IF(ISBLANK(B504),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B504))</f>
         <v/>
@@ -10842,7 +10869,7 @@
       <c r="F504" s="13"/>
       <c r="G504" s="45"/>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="74" t="str">
         <f>IF(ISBLANK(B505),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B505))</f>
         <v/>
@@ -10854,7 +10881,7 @@
       <c r="F505" s="14"/>
       <c r="G505" s="46"/>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="73" t="str">
         <f>IF(ISBLANK(B506),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B506))</f>
         <v/>
@@ -10866,7 +10893,7 @@
       <c r="F506" s="13"/>
       <c r="G506" s="45"/>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="74" t="str">
         <f>IF(ISBLANK(B507),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B507))</f>
         <v/>
@@ -10878,7 +10905,7 @@
       <c r="F507" s="14"/>
       <c r="G507" s="46"/>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="73" t="str">
         <f>IF(ISBLANK(B508),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B508))</f>
         <v/>
@@ -10890,7 +10917,7 @@
       <c r="F508" s="13"/>
       <c r="G508" s="45"/>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="74" t="str">
         <f>IF(ISBLANK(B509),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B509))</f>
         <v/>
@@ -10902,7 +10929,7 @@
       <c r="F509" s="14"/>
       <c r="G509" s="46"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="73" t="str">
         <f>IF(ISBLANK(B510),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B510))</f>
         <v/>
@@ -10914,7 +10941,7 @@
       <c r="F510" s="13"/>
       <c r="G510" s="45"/>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="74" t="str">
         <f>IF(ISBLANK(B511),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B511))</f>
         <v/>
@@ -10926,7 +10953,7 @@
       <c r="F511" s="14"/>
       <c r="G511" s="46"/>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="73" t="str">
         <f>IF(ISBLANK(B512),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B512))</f>
         <v/>
@@ -10938,7 +10965,7 @@
       <c r="F512" s="13"/>
       <c r="G512" s="45"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="74" t="str">
         <f>IF(ISBLANK(B513),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B513))</f>
         <v/>
@@ -10950,7 +10977,7 @@
       <c r="F513" s="14"/>
       <c r="G513" s="46"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="73" t="str">
         <f>IF(ISBLANK(B514),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B514))</f>
         <v/>
@@ -10962,7 +10989,7 @@
       <c r="F514" s="13"/>
       <c r="G514" s="45"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="74" t="str">
         <f>IF(ISBLANK(B515),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B515))</f>
         <v/>
@@ -10974,7 +11001,7 @@
       <c r="F515" s="14"/>
       <c r="G515" s="46"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="73" t="str">
         <f>IF(ISBLANK(B516),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B516))</f>
         <v/>
@@ -10986,7 +11013,7 @@
       <c r="F516" s="13"/>
       <c r="G516" s="45"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="74" t="str">
         <f>IF(ISBLANK(B517),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B517))</f>
         <v/>
@@ -10998,7 +11025,7 @@
       <c r="F517" s="14"/>
       <c r="G517" s="46"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="73" t="str">
         <f>IF(ISBLANK(B518),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B518))</f>
         <v/>
@@ -11010,7 +11037,7 @@
       <c r="F518" s="13"/>
       <c r="G518" s="45"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="74" t="str">
         <f>IF(ISBLANK(B519),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B519))</f>
         <v/>
@@ -11022,7 +11049,7 @@
       <c r="F519" s="14"/>
       <c r="G519" s="46"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="73" t="str">
         <f>IF(ISBLANK(B520),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B520))</f>
         <v/>
@@ -11034,7 +11061,7 @@
       <c r="F520" s="13"/>
       <c r="G520" s="45"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="74" t="str">
         <f>IF(ISBLANK(B521),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B521))</f>
         <v/>
@@ -11046,7 +11073,7 @@
       <c r="F521" s="14"/>
       <c r="G521" s="46"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="73" t="str">
         <f>IF(ISBLANK(B522),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B522))</f>
         <v/>
@@ -11058,7 +11085,7 @@
       <c r="F522" s="13"/>
       <c r="G522" s="45"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="74" t="str">
         <f>IF(ISBLANK(B523),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B523))</f>
         <v/>
@@ -11070,7 +11097,7 @@
       <c r="F523" s="14"/>
       <c r="G523" s="46"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="73" t="str">
         <f>IF(ISBLANK(B524),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B524))</f>
         <v/>
@@ -11082,7 +11109,7 @@
       <c r="F524" s="13"/>
       <c r="G524" s="45"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="74" t="str">
         <f>IF(ISBLANK(B525),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B525))</f>
         <v/>
@@ -11094,7 +11121,7 @@
       <c r="F525" s="14"/>
       <c r="G525" s="46"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="73" t="str">
         <f>IF(ISBLANK(B526),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B526))</f>
         <v/>
@@ -11106,7 +11133,7 @@
       <c r="F526" s="13"/>
       <c r="G526" s="45"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="74" t="str">
         <f>IF(ISBLANK(B527),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B527))</f>
         <v/>
@@ -11118,7 +11145,7 @@
       <c r="F527" s="14"/>
       <c r="G527" s="46"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="73" t="str">
         <f>IF(ISBLANK(B528),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B528))</f>
         <v/>
@@ -11130,7 +11157,7 @@
       <c r="F528" s="13"/>
       <c r="G528" s="45"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="74" t="str">
         <f>IF(ISBLANK(B529),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B529))</f>
         <v/>
@@ -11142,7 +11169,7 @@
       <c r="F529" s="14"/>
       <c r="G529" s="46"/>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="73" t="str">
         <f>IF(ISBLANK(B530),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B530))</f>
         <v/>
@@ -11154,7 +11181,7 @@
       <c r="F530" s="13"/>
       <c r="G530" s="45"/>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="74" t="str">
         <f>IF(ISBLANK(B531),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B531))</f>
         <v/>
@@ -11166,7 +11193,7 @@
       <c r="F531" s="14"/>
       <c r="G531" s="46"/>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="73" t="str">
         <f>IF(ISBLANK(B532),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B532))</f>
         <v/>
@@ -11235,7 +11262,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21D7432-C939-0D45-BAC2-A6A2196EA9C6}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:N12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="10.875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
@@ -11247,7 +11274,7 @@
     <col min="14" max="14" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E2" s="77" t="s">
         <v>60</v>
       </c>
@@ -11261,12 +11288,12 @@
       <c r="M2" s="52"/>
       <c r="N2" s="20"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L3" s="24"/>
       <c r="M3" s="25"/>
       <c r="N3" s="24"/>
     </row>
-    <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E4" s="77" t="s">
         <v>62</v>
       </c>
@@ -11276,7 +11303,7 @@
       <c r="M4" s="48"/>
       <c r="N4" s="24"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -11306,7 +11333,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -11329,7 +11356,7 @@
       </c>
       <c r="G6" s="47">
         <f>SUM(A6:B6)/$C$10</f>
-        <v>7.7809798270893377E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="L6" s="62" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11343,18 +11370,18 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>720</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>1590</v>
+        <v>1610</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11362,11 +11389,11 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>26 h 30 min</v>
+        <v>26 h 50 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
-        <v>0.91642651296829969</v>
+        <v>0.85866666666666669</v>
       </c>
       <c r="L7" s="64" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11380,7 +11407,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E8,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -11417,10 +11444,10 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
@@ -11428,7 +11455,7 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="E9" s="23" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11436,11 +11463,11 @@
       </c>
       <c r="F9" s="55" t="str">
         <f t="shared" si="1"/>
-        <v>0 h 10 min</v>
+        <v>2 h 10 min</v>
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>5.763688760806916E-3</v>
+        <v>6.933333333333333E-2</v>
       </c>
       <c r="L9" s="66" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11454,29 +11481,29 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>720</v>
+        <v>840</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>28 h 55 min</v>
+        <v>31 h 15 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.32859848484848486</v>
+        <v>0.35511363636363635</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>70</v>
@@ -11487,13 +11514,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C11">
         <f>F2*60</f>
         <v>5280</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F12" s="51"/>
     </row>
   </sheetData>
@@ -11506,7 +11533,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F31118-7D2C-C547-B9C9-EA2B04E048B8}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection algorithmName="SHA-512" hashValue="XbZXOKbfSAgLNZr8i9zbx3Mg5WERmkYtMQ92zj4MzR65FvyWSSvnn71Zle3H3OLpYxxTtkJ9EnrqgX4Va8ga5w==" saltValue="TZrTQ2fJcSarc1EkKUon9w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11515,6 +11542,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11727,15 +11763,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11749,6 +11776,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11767,14 +11802,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>
